--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,11 +145,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
@@ -261,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -332,25 +327,22 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1612,7 +1604,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1744,7 +1736,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1801,38 +1793,30 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>92299060</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>49358</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="5" t="n">
+        <v>92299060</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>49358</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1825,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1855,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1946,7 +1930,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -2008,7 +1992,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2070,7 +2054,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2132,7 +2116,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2194,7 +2178,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2256,7 +2240,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2388,7 +2372,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2450,7 +2434,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2512,7 +2496,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2574,7 +2558,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2636,7 +2620,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2698,7 +2682,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2760,7 +2744,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2822,7 +2806,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2884,7 +2868,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2946,7 +2930,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3008,7 +2992,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3070,7 +3054,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3132,7 +3116,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3256,7 +3240,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3318,7 +3302,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3380,7 +3364,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3442,7 +3426,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3504,7 +3488,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3566,7 +3550,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3628,7 +3612,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3690,7 +3674,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3752,7 +3736,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2023-01-20</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3814,7 +3798,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3876,7 +3860,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3938,7 +3922,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4000,7 +3984,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4062,7 +4046,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4124,7 +4108,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4186,7 +4170,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4248,7 +4232,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4310,7 +4294,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4372,7 +4356,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4434,7 +4418,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4496,7 +4480,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4558,7 +4542,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4620,7 +4604,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -5382,7 +5366,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5444,7 +5428,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5786,7 +5770,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5988,7 +5972,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6120,7 +6104,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6252,7 +6236,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6384,7 +6368,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6446,7 +6430,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6508,7 +6492,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6640,7 +6624,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6702,7 +6686,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6764,7 +6748,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6896,7 +6880,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6958,7 +6942,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7020,7 +7004,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7082,7 +7066,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7144,7 +7128,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7206,7 +7190,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7268,7 +7252,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7330,7 +7314,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7392,7 +7376,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7454,7 +7438,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7516,7 +7500,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7578,7 +7562,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7640,7 +7624,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7702,7 +7686,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7764,7 +7748,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7826,7 +7810,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7888,7 +7872,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7950,7 +7934,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8012,7 +7996,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8074,7 +8058,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8136,7 +8120,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8198,7 +8182,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8260,7 +8244,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8322,7 +8306,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8384,7 +8368,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8446,7 +8430,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8508,7 +8492,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8570,7 +8554,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8632,7 +8616,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8834,7 +8818,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8896,7 +8880,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9098,7 +9082,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9160,7 +9144,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9642,7 +9626,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9704,7 +9688,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9906,7 +9890,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9968,7 +9952,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10170,7 +10154,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10232,7 +10216,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10434,7 +10418,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10496,7 +10480,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10698,7 +10682,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10760,7 +10744,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10892,7 +10876,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10954,7 +10938,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11016,7 +11000,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11148,7 +11132,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11210,7 +11194,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11272,7 +11256,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11404,7 +11388,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11466,7 +11450,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11528,7 +11512,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11730,7 +11714,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11792,7 +11776,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11994,7 +11978,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12056,7 +12040,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12258,7 +12242,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12320,7 +12304,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12522,7 +12506,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12584,7 +12568,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12786,7 +12770,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12848,7 +12832,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13050,7 +13034,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13112,7 +13096,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13314,7 +13298,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13376,7 +13360,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13508,7 +13492,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13570,7 +13554,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13632,7 +13616,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13764,7 +13748,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13826,7 +13810,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13888,7 +13872,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14090,7 +14074,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14152,7 +14136,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14354,7 +14338,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14416,7 +14400,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14618,7 +14602,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14680,7 +14664,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14882,7 +14866,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14944,7 +14928,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15216,7 +15200,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15488,7 +15472,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15760,7 +15744,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16032,7 +16016,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16304,7 +16288,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16576,7 +16560,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16708,7 +16692,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16770,7 +16754,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16832,7 +16816,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16894,7 +16878,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16956,7 +16940,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17018,7 +17002,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17080,7 +17064,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17142,7 +17126,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17204,7 +17188,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17266,7 +17250,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17328,7 +17312,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17390,7 +17374,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17452,7 +17436,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17514,7 +17498,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17576,7 +17560,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17638,7 +17622,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17700,7 +17684,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17762,7 +17746,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17824,7 +17808,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17886,7 +17870,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17948,7 +17932,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18010,7 +17994,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -18072,7 +18056,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18134,7 +18118,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18196,7 +18180,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18258,7 +18242,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18320,7 +18304,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18382,7 +18366,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18444,7 +18428,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18506,7 +18490,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18568,7 +18552,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18630,7 +18614,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18692,7 +18676,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18754,7 +18738,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18816,7 +18800,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18878,7 +18862,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18940,7 +18924,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19002,7 +18986,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19064,7 +19048,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19126,7 +19110,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19188,7 +19172,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19250,7 +19234,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -19312,7 +19296,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19369,30 +19353,38 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="H289" s="5" t="n">
-        <v>12909600</v>
-      </c>
-      <c r="I289" s="5" t="n">
-        <v>24684</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K289" s="5" t="n">
-        <v>12909600</v>
-      </c>
-      <c r="L289" s="5" t="n">
-        <v>24684</v>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -19401,7 +19393,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19436,7 +19428,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19498,7 +19490,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19560,7 +19552,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19622,7 +19614,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19684,7 +19676,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19746,7 +19738,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19808,7 +19800,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19870,7 +19862,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19932,7 +19924,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19994,7 +19986,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20056,7 +20048,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20118,7 +20110,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20180,7 +20172,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -20242,7 +20234,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20304,7 +20296,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20366,7 +20358,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20428,7 +20420,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20490,7 +20482,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20552,7 +20544,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20614,7 +20606,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20676,7 +20668,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20738,7 +20730,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20800,7 +20792,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20862,7 +20854,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20924,7 +20916,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20986,7 +20978,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21048,7 +21040,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21110,7 +21102,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21172,7 +21164,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -21234,7 +21226,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21296,7 +21288,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21358,7 +21350,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -21420,7 +21412,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21482,7 +21474,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21544,7 +21536,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21606,7 +21598,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21668,7 +21660,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21730,7 +21722,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21792,7 +21784,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21854,7 +21846,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21916,7 +21908,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21978,7 +21970,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22040,7 +22032,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22102,7 +22094,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22164,7 +22156,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22226,7 +22218,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22358,7 +22350,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22420,7 +22412,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22482,7 +22474,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -22544,7 +22536,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22606,7 +22598,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22668,7 +22660,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22730,7 +22722,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22792,7 +22784,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22854,7 +22846,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22916,7 +22908,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22978,7 +22970,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23040,7 +23032,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23102,7 +23094,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23164,7 +23156,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -23226,7 +23218,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23288,7 +23280,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23350,7 +23342,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -23412,7 +23404,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23474,7 +23466,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23536,7 +23528,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23598,7 +23590,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23660,7 +23652,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -23722,7 +23714,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23784,7 +23776,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23846,7 +23838,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23908,7 +23900,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23970,7 +23962,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24032,7 +24024,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -24094,7 +24086,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -24156,7 +24148,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -24218,7 +24210,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -24280,7 +24272,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24342,7 +24334,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24404,7 +24396,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24466,7 +24458,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24528,7 +24520,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24590,7 +24582,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24652,7 +24644,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24714,7 +24706,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24776,7 +24768,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24838,7 +24830,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24900,7 +24892,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24962,7 +24954,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -25024,7 +25016,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25086,7 +25078,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -25148,7 +25140,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -25210,7 +25202,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25272,7 +25264,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -25334,7 +25326,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25396,7 +25388,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25458,7 +25450,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25520,7 +25512,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25582,7 +25574,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25644,7 +25636,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25706,7 +25698,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25768,7 +25760,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25830,7 +25822,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25892,7 +25884,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25954,7 +25946,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -26016,7 +26008,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -26078,7 +26070,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -26140,7 +26132,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -26202,7 +26194,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -26264,7 +26256,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -26326,7 +26318,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -26388,7 +26380,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -26450,7 +26442,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26512,7 +26504,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26574,7 +26566,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26636,7 +26628,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26698,7 +26690,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -26760,7 +26752,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -26822,7 +26814,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26884,7 +26876,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26946,7 +26938,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -27008,7 +27000,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -27070,7 +27062,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -27132,7 +27124,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -27194,7 +27186,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -27256,7 +27248,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -27318,7 +27310,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -27380,7 +27372,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -27442,7 +27434,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -27504,7 +27496,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -27566,7 +27558,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -27628,7 +27620,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -27690,7 +27682,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27752,7 +27744,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27814,7 +27806,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27876,7 +27868,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -28008,7 +28000,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -28070,7 +28062,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -28132,7 +28124,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -28194,7 +28186,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -28256,7 +28248,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -28318,7 +28310,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -28380,7 +28372,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -28442,7 +28434,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -28504,7 +28496,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -28566,7 +28558,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -28628,7 +28620,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -28690,7 +28682,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -28752,7 +28744,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -28814,7 +28806,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28876,7 +28868,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28938,7 +28930,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -29000,7 +28992,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -29062,7 +29054,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -29124,7 +29116,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -29186,7 +29178,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -29248,7 +29240,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -29310,7 +29302,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -29372,7 +29364,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -29434,7 +29426,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -29496,7 +29488,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -29558,7 +29550,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -29620,7 +29612,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -29682,7 +29674,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29744,7 +29736,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -29806,7 +29798,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -29868,7 +29860,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29930,7 +29922,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-14</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29992,7 +29984,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -30054,7 +30046,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -30116,7 +30108,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2023-03-06</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -30178,7 +30170,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -30240,7 +30232,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -30302,7 +30294,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -30364,7 +30356,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -30426,7 +30418,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -30488,7 +30480,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -30550,7 +30542,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -30612,7 +30604,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -30674,7 +30666,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -30736,7 +30728,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -30798,7 +30790,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -30860,7 +30852,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2022-12-28</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30922,7 +30914,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30984,7 +30976,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -31046,7 +31038,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -31108,7 +31100,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -31170,7 +31162,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -31232,7 +31224,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -31294,7 +31286,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -31356,7 +31348,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2022-12-21</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -31418,7 +31410,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -31480,7 +31472,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -31542,7 +31534,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -31604,7 +31596,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -31666,7 +31658,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -31728,7 +31720,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -31790,7 +31782,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -31852,7 +31844,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31914,7 +31906,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -31976,7 +31968,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -32038,7 +32030,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -32100,7 +32092,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -32162,7 +32154,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -32224,7 +32216,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -32286,7 +32278,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -32348,7 +32340,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -32410,7 +32402,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -32472,7 +32464,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -32534,7 +32526,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -32596,7 +32588,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -32658,7 +32650,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -32720,7 +32712,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -32782,7 +32774,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -32844,7 +32836,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -32906,7 +32898,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32968,7 +32960,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -33030,7 +33022,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -33092,7 +33084,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -33154,7 +33146,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -33216,7 +33208,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -33278,7 +33270,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -33340,7 +33332,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -33402,7 +33394,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -33464,7 +33456,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -33526,7 +33518,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -33588,7 +33580,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -33650,7 +33642,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -33712,7 +33704,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -33774,7 +33766,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -33836,7 +33828,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -33898,7 +33890,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -33960,7 +33952,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -34022,7 +34014,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -34084,7 +34076,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -34146,7 +34138,7 @@
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H527" s="5" t="n">
@@ -34208,7 +34200,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -34270,7 +34262,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -34332,7 +34324,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -34394,7 +34386,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -34456,7 +34448,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -34518,7 +34510,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -34580,7 +34572,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -34642,7 +34634,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -34704,7 +34696,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -34766,7 +34758,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -34828,7 +34820,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -34890,7 +34882,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -34952,7 +34944,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -35014,7 +35006,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -35076,7 +35068,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -35138,7 +35130,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2023-02-21</t>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -35200,7 +35192,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -35262,7 +35254,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2023-02-21</t>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -35324,7 +35316,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -35386,7 +35378,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -35448,7 +35440,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -35510,7 +35502,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -35572,7 +35564,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -35634,7 +35626,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -35696,7 +35688,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -35758,7 +35750,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -35820,7 +35812,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -35882,7 +35874,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -35944,7 +35936,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -36006,7 +35998,7 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
@@ -36068,7 +36060,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -36130,7 +36122,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2023-02-22</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -36192,7 +36184,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -36254,7 +36246,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -36316,7 +36308,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -36378,7 +36370,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -36440,7 +36432,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -36502,7 +36494,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -36564,7 +36556,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -36626,7 +36618,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -36688,7 +36680,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -36750,7 +36742,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -36812,7 +36804,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -36874,7 +36866,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -36936,7 +36928,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -36998,7 +36990,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -37060,7 +37052,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -37122,7 +37114,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -37184,7 +37176,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -37246,7 +37238,7 @@
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H577" s="5" t="n">
@@ -37308,7 +37300,7 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H578" s="5" t="n">
@@ -37370,7 +37362,7 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H579" s="5" t="n">
@@ -37432,7 +37424,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -37813,17 +37805,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37957,7 +37949,7 @@
           <t>A | 2088呎 (4+房)
 $12605万
 $60,370/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -37980,7 +37972,7 @@
           <t>A | 2034呎 (4+房)
 $12522万
 $61,562/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38003,7 +37995,7 @@
           <t>A | 2088呎 (4+房)
 $12446万
 $59,609/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38021,20 +38013,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-招标单位
--
-(已定价未售)</t>
+$9230万
+$49,358/呎
+(26年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -38049,7 +38041,7 @@
           <t>A | 2088呎 (4+房)
 $11761万
 $56,327/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -38057,7 +38049,7 @@
           <t>B | 1870呎 (4+房)
 $9483万
 $50,710/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -38072,7 +38064,7 @@
           <t>A | 2088呎 (4+房)
 $12055万
 $57,737/呎
-(23年-03月-14日)</t>
+(23年-03月-15日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -38080,7 +38072,7 @@
           <t>B | 1870呎 (4+房)
 $8796万
 $47,036/呎
-(23年-03月-14日)</t>
+(23年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -38095,7 +38087,7 @@
           <t>A | 2088呎 (4+房)
 $11467万
 $54,916/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -38103,7 +38095,7 @@
           <t>B | 1870呎 (4+房)
 $9233万
 $49,376/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -38118,7 +38110,7 @@
           <t>A | 2088呎 (4+房)
 $10557万
 $50,561/呎
-(23年-02月-07日)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38141,7 +38133,7 @@
           <t>A | 2088呎 (4+房)
 $12038万
 $57,653/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -38149,7 +38141,7 @@
           <t>B | 1870呎 (4+房)
 $9278万
 $49,617/呎
-(26年-07月-03日)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -38164,7 +38156,7 @@
           <t>A | 2088呎 (4+房)
 $10255万
 $49,113/呎
-(23年-02月-02日)</t>
+(23年-02月-03日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -38172,7 +38164,7 @@
           <t>B | 1870呎 (4+房)
 $8013万
 $42,850/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -38187,7 +38179,7 @@
           <t>A | 2088呎 (4+房)
 $10110万
 $48,419/呎
-(23年-01月-30日)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -38195,7 +38187,7 @@
           <t>B | 1816呎 (4+房)
 $9054万
 $49,856/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -38210,7 +38202,7 @@
           <t>A | 2088呎 (4+房)
 $10252万
 $49,100/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -38218,7 +38210,7 @@
           <t>B | 1870呎 (4+房)
 $8578万
 $45,870/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38225,7 @@
           <t>A | 2088呎 (4+房)
 $10085万
 $48,300/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -38241,7 +38233,7 @@
           <t>B | 1870呎 (4+房)
 $8929万
 $47,748/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38248,7 @@
           <t>A | 2088呎 (4+房)
 $10117万
 $48,453/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -38264,7 +38256,7 @@
           <t>B | 1816呎 (4+房)
 $8690万
 $47,852/呎
-(26年-06月-28日)</t>
+(26年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38271,7 @@
           <t>A | 2088呎 (4+房)
 $9855万
 $47,200/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -38287,7 +38279,7 @@
           <t>B | 1870呎 (4+房)
 $8308万
 $44,429/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -38302,7 +38294,7 @@
           <t>A | 2088呎 (4+房)
 $9587万
 $45,913/呎
-(23年-02月-14日)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -38310,7 +38302,7 @@
           <t>B | 1870呎 (4+房)
 $8207万
 $43,889/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38317,7 @@
           <t>A | 2088呎 (4+房)
 $9324万
 $44,653/呎
-(23年-01月-30日)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -38333,7 +38325,7 @@
           <t>B | 1870呎 (4+房)
 $8477万
 $45,333/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38340,7 @@
           <t>A | 2088呎 (4+房)
 $9542万
 $45,700/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -38356,7 +38348,7 @@
           <t>B | 1870呎 (4+房)
 $7386万
 $39,500/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -38371,7 +38363,7 @@
           <t>A | 2088呎 (4+房)
 $9420万
 $45,115/呎
-(23年-01月-19日)</t>
+(23年-01月-20日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -38379,7 +38371,7 @@
           <t>B | 1870呎 (4+房)
 $7939万
 $42,457/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38386,7 @@
           <t>A | 2088呎 (4+房)
 $8403万
 $40,242/呎
-(23年-01月-12日)</t>
+(23年-01月-13日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -38402,7 +38394,7 @@
           <t>B | 1870呎 (4+房)
 $7315万
 $39,120/呎
-(23年-01月-12日)</t>
+(23年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -38417,7 +38409,7 @@
           <t>A | 2088呎 (4+房)
 $8456万
 $40,500/呎
-(23年-03月-01日)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -38425,7 +38417,7 @@
           <t>B | 1870呎 (4+房)
 $7143万
 $38,200/呎
-(23年-03月-01日)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -38440,7 +38432,7 @@
           <t>A | 2088呎 (4+房)
 $9271万
 $44,400/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -38448,7 +38440,7 @@
           <t>B | 1870呎 (4+房)
 $8182万
 $43,753/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -38463,7 +38455,7 @@
           <t>A | 2088呎 (4+房)
 $9703万
 $46,472/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -38471,7 +38463,7 @@
           <t>B | 1870呎 (4+房)
 $7750万
 $41,444/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -38486,7 +38478,7 @@
           <t>A | 2088呎 (4+房)
 $9127万
 $43,710/呎
-(23年-03月-14日)</t>
+(23年-03月-15日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -38494,7 +38486,7 @@
           <t>B | 1870呎 (4+房)
 $7696万
 $41,157/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -38509,7 +38501,7 @@
           <t>A | 2088呎 (4+房)
 $9427万
 $45,150/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -38517,7 +38509,7 @@
           <t>B | 1870呎 (4+房)
 $7684万
 $41,089/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -38532,7 +38524,7 @@
           <t>A | 1985呎 (4+房)
 $8658万
 $43,617/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -38540,7 +38532,7 @@
           <t>B | 1797呎 (4+房)
 $7178万
 $39,946/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -38781,7 +38773,7 @@
           <t>A | 1909呎 (4+房)
 $9704万
 $50,832/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -38789,7 +38781,7 @@
           <t>B | 1870呎 (4+房)
 $9146万
 $48,910/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -38858,7 +38850,7 @@
           <t>B | 1870呎 (4+房)
 $8415万
 $45,000/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -38873,7 +38865,7 @@
           <t>A | 1909呎 (4+房)
 $9434万
 $49,421/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38896,7 +38888,7 @@
           <t>A | 1909呎 (4+房)
 $9490万
 $49,712/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38919,7 +38911,7 @@
           <t>A | 1909呎 (4+房)
 $8880万
 $46,517/呎
-(23年-02月-12日)</t>
+(23年-02月-13日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38942,7 +38934,7 @@
           <t>A | 1909呎 (4+房)
 $9295万
 $48,690/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38965,7 +38957,7 @@
           <t>A | 1909呎 (4+房)
 $9015万
 $47,221/呎
-(23年-07月-05日)</t>
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -38973,7 +38965,7 @@
           <t>B | 1816呎 (4+房)
 $9086万
 $50,033/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -38988,7 +38980,7 @@
           <t>A | 1909呎 (4+房)
 $9017万
 $47,236/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39011,7 +39003,7 @@
           <t>A | 1909呎 (4+房)
 $8552万
 $44,800/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -39019,7 +39011,7 @@
           <t>B | 1870呎 (4+房)
 $8265万
 $44,200/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -39034,7 +39026,7 @@
           <t>A | 1909呎 (4+房)
 $8837万
 $46,290/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -39057,7 +39049,7 @@
           <t>A | 1909呎 (4+房)
 $8302万
 $43,490/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -39065,7 +39057,7 @@
           <t>B | 1870呎 (4+房)
 $8103万
 $43,329/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -39080,7 +39072,7 @@
           <t>A | 1909呎 (4+房)
 $7865万
 $41,200/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -39088,7 +39080,7 @@
           <t>B | 1870呎 (4+房)
 $7667万
 $41,000/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -39103,7 +39095,7 @@
           <t>A | 1909呎 (4+房)
 $7770万
 $40,700/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -39111,7 +39103,7 @@
           <t>B | 1870呎 (4+房)
 $7574万
 $40,500/呎
-(24年-08月-06日)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -39126,7 +39118,7 @@
           <t>A | 1909呎 (4+房)
 $8062万
 $42,231/呎
-(24年-07月-21日)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -39134,7 +39126,7 @@
           <t>B | 1870呎 (4+房)
 $8054万
 $43,070/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39141,7 @@
           <t>A | 1909呎 (4+房)
 $8319万
 $43,579/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -39157,7 +39149,7 @@
           <t>B | 1870呎 (4+房)
 $7630万
 $40,800/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -39172,7 +39164,7 @@
           <t>A | 1909呎 (4+房)
 $7882万
 $41,290/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -39180,7 +39172,7 @@
           <t>B | 1870呎 (4+房)
 $7904万
 $42,270/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -39195,7 +39187,7 @@
           <t>A | 1909呎 (4+房)
 $7470万
 $39,130/呎
-(23年-07月-05日)</t>
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -39203,7 +39195,7 @@
           <t>B | 1870呎 (4+房)
 $7860万
 $42,029/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -39218,7 +39210,7 @@
           <t>A | 1909呎 (4+房)
 $8131万
 $42,595/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -39226,7 +39218,7 @@
           <t>B | 1870呎 (4+房)
 $7800万
 $41,710/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -39241,7 +39233,7 @@
           <t>A | 1909呎 (4+房)
 $8104万
 $42,453/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -39249,7 +39241,7 @@
           <t>B | 1870呎 (4+房)
 $8167万
 $43,673/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -39264,7 +39256,7 @@
           <t>A | 1909呎 (4+房)
 $7708万
 $40,377/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -39272,7 +39264,7 @@
           <t>B | 1870呎 (4+房)
 $7532万
 $40,276/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -39287,7 +39279,7 @@
           <t>A | 1909呎 (4+房)
 $7292万
 $38,200/呎
-(24年-06月-19日)</t>
+(24年-06月-20日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -39295,7 +39287,7 @@
           <t>B | 1870呎 (4+房)
 $7704万
 $41,196/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -39310,7 +39302,7 @@
           <t>A | 1909呎 (4+房)
 $7576万
 $39,687/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -39318,7 +39310,7 @@
           <t>B | 1816呎 (4+房)
 $7996万
 $44,028/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -39333,7 +39325,7 @@
           <t>A | 1828呎 (4+房)
 $7534万
 $41,213/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -39341,7 +39333,7 @@
           <t>B | 1797呎 (4+房)
 $7380万
 $41,069/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -39479,7 +39471,7 @@
           <t>A | 1129呎 (3房)
 $5215万
 $46,195/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -39487,11 +39479,11 @@
           <t>B | 1334呎 (3房)
 $3869万
 $29,000/呎
-(26年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="inlineStr"/>
-      <c r="E5" s="25" t="inlineStr"/>
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="E5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -39504,7 +39496,7 @@
           <t>A | 577呎 (2房)
 $1546万
 $26,800/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -39512,7 +39504,7 @@
           <t>B | 553呎 (2房)
 $1391万
 $25,145/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -39543,7 +39535,7 @@
           <t>A | 577呎 (2房)
 $1512万
 $26,200/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -39551,7 +39543,7 @@
           <t>B | 553呎 (2房)
 $1363万
 $24,644/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -39621,7 +39613,7 @@
           <t>A | 577呎 (2房)
 $1489万
 $25,810/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -39629,7 +39621,7 @@
           <t>B | 554呎 (2房)
 $1324万
 $23,900/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -39660,7 +39652,7 @@
           <t>A | 577呎 (2房)
 $1482万
 $25,681/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -39668,7 +39660,7 @@
           <t>B | 553呎 (2房)
 $1319万
 $23,843/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -39699,7 +39691,7 @@
           <t>A | 577呎 (2房)
 $1474万
 $25,554/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -39707,7 +39699,7 @@
           <t>B | 553呎 (2房)
 $1341万
 $24,244/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -39738,7 +39730,7 @@
           <t>A | 577呎 (2房)
 $1467万
 $25,426/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -39746,7 +39738,7 @@
           <t>B | 554呎 (2房)
 $1335万
 $24,100/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -39777,7 +39769,7 @@
           <t>A | 577呎 (2房)
 $1460万
 $25,300/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -39785,7 +39777,7 @@
           <t>B | 554呎 (2房)
 $1319万
 $23,800/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -39816,7 +39808,7 @@
           <t>A | 577呎 (2房)
 $1469万
 $25,454/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -39824,7 +39816,7 @@
           <t>B | 554呎 (2房)
 $1285万
 $23,200/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -39832,7 +39824,7 @@
           <t>C | 509呎 (2房)
 $1196万
 $23,500/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -39855,7 +39847,7 @@
           <t>A | 577呎 (2房)
 $1438万
 $24,925/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -39863,7 +39855,7 @@
           <t>B | 554呎 (2房)
 $1274万
 $23,000/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -39871,7 +39863,7 @@
           <t>C | 509呎 (2房)
 $1191万
 $23,400/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -39894,7 +39886,7 @@
           <t>A | 577呎 (2房)
 $1431万
 $24,801/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -39902,7 +39894,7 @@
           <t>B | 554呎 (2房)
 $1269万
 $22,900/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -39910,7 +39902,7 @@
           <t>C | 509呎 (2房)
 $1186万
 $23,300/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -39933,7 +39925,7 @@
           <t>A | 577呎 (2房)
 $1424万
 $24,677/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -39941,7 +39933,7 @@
           <t>B | 553呎 (2房)
 $1302万
 $23,542/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -39972,7 +39964,7 @@
           <t>A | 577呎 (2房)
 $1417万
 $24,555/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -39980,7 +39972,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -40011,7 +40003,7 @@
           <t>A | 577呎 (2房)
 $1410万
 $24,432/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -40019,7 +40011,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -40050,7 +40042,7 @@
           <t>A | 577呎 (2房)
 $1403万
 $24,311/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -40058,7 +40050,7 @@
           <t>B | 553呎 (2房)
 $1285万
 $23,242/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -40089,7 +40081,7 @@
           <t>A | 577呎 (2房)
 $1411万
 $24,459/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -40097,7 +40089,7 @@
           <t>B | 554呎 (2房)
 $1280万
 $23,100/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -40128,7 +40120,7 @@
           <t>A | 577呎 (2房)
 $1389万
 $24,070/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -40136,7 +40128,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -40167,7 +40159,7 @@
           <t>A | 577呎 (2房)
 $1382万
 $23,950/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -40175,7 +40167,7 @@
           <t>B | 553呎 (2房)
 $1274万
 $23,042/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -40206,7 +40198,7 @@
           <t>A | 577呎 (2房)
 $1368万
 $23,713/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -40214,7 +40206,7 @@
           <t>B | 554呎 (2房)
 $1258万
 $22,700/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -40222,7 +40214,7 @@
           <t>C | 509呎 (2房)
 $1155万
 $22,700/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40245,7 +40237,7 @@
           <t>A | 577呎 (2房)
 $1361万
 $23,595/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -40253,7 +40245,7 @@
           <t>B | 553呎 (2房)
 $1252万
 $22,641/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -40261,7 +40253,7 @@
           <t>C | 509呎 (2房)
 $1150万
 $22,600/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -40284,7 +40276,7 @@
           <t>A | 577呎 (2房)
 $1355万
 $23,477/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -40292,7 +40284,7 @@
           <t>B | 554呎 (2房)
 $1295万
 $23,377/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -40323,7 +40315,7 @@
           <t>A | 577呎 (2房)
 $1348万
 $23,361/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -40331,7 +40323,7 @@
           <t>B | 553呎 (2房)
 $1252万
 $22,641/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -40362,7 +40354,7 @@
           <t>A | 577呎 (2房)
 $1341万
 $23,244/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -40370,7 +40362,7 @@
           <t>B | 554呎 (2房)
 $1246万
 $22,500/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -40401,7 +40393,7 @@
           <t>A | 577呎 (2房)
 $1335万
 $23,129/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -40409,7 +40401,7 @@
           <t>B | 554呎 (2房)
 $1235万
 $22,300/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -40440,7 +40432,7 @@
           <t>A | 577呎 (2房)
 $1247万
 $21,606/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -40479,7 +40471,7 @@
           <t>A | 577呎 (2房)
 $1210万
 $20,976/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -40518,7 +40510,7 @@
           <t>A | 577呎 (2房)
 $1198万
 $20,769/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -40557,7 +40549,7 @@
           <t>A | 577呎 (2房)
 $1195万
 $20,706/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -40596,7 +40588,7 @@
           <t>A | 577呎 (2房)
 $1191万
 $20,644/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -40635,7 +40627,7 @@
           <t>A | 539呎 (2房)
 $1197万
 $22,200/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -40734,7 +40726,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40744,7 +40736,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40794,8 +40786,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr"/>
-      <c r="D5" s="25" t="inlineStr"/>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -40808,7 +40800,7 @@
           <t>A | 659呎 (2房)
 $1799万
 $27,300/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -40816,7 +40808,7 @@
           <t>B | 523呎 (2房)
 $1423万
 $27,200/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -40824,7 +40816,7 @@
           <t>C | 568呎 (2房)
 $1551万
 $27,300/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -40839,7 +40831,7 @@
           <t>A | 659呎 (2房)
 $1766万
 $26,800/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -40847,7 +40839,7 @@
           <t>B | 523呎 (2房)
 $1396万
 $26,700/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -40855,7 +40847,7 @@
           <t>C | 568呎 (2房)
 $1522万
 $26,800/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -40870,7 +40862,7 @@
           <t>A | 659呎 (2房)
 $1746万
 $26,500/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -40878,7 +40870,7 @@
           <t>B | 523呎 (2房)
 $1381万
 $26,400/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -40886,7 +40878,7 @@
           <t>C | 568呎 (2房)
 $1505万
 $26,500/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -40901,7 +40893,7 @@
           <t>A | 659呎 (2房)
 $1735万
 $26,323/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -40909,7 +40901,7 @@
           <t>B | 523呎 (2房)
 $1371万
 $26,205/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -40917,7 +40909,7 @@
           <t>C | 1644呎 (2房)
 $1496万
 $9,099/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -40932,7 +40924,7 @@
           <t>A | 659呎 (2房)
 $1726万
 $26,192/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -40940,7 +40932,7 @@
           <t>B | 523呎 (2房)
 $1364万
 $26,075/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -40948,7 +40940,7 @@
           <t>C | 568呎 (2房)
 $1488万
 $26,205/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -40963,7 +40955,7 @@
           <t>A | 659呎 (2房)
 $1717万
 $26,062/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -40971,7 +40963,7 @@
           <t>B | 523呎 (2房)
 $1357万
 $25,945/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -40979,7 +40971,7 @@
           <t>C | 568呎 (2房)
 $1481万
 $26,075/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -40994,7 +40986,7 @@
           <t>A | 659呎 (2房)
 $1709万
 $25,932/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -41002,7 +40994,7 @@
           <t>B | 523呎 (2房)
 $1350万
 $25,816/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -41010,7 +41002,7 @@
           <t>C | 568呎 (2房)
 $1474万
 $25,945/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -41025,7 +41017,7 @@
           <t>A | 659呎 (2房)
 $1700万
 $25,803/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -41033,7 +41025,7 @@
           <t>B | 523呎 (2房)
 $1343万
 $25,688/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -41041,7 +41033,7 @@
           <t>C | 568呎 (2房)
 $1466万
 $25,816/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41048,7 @@
           <t>A | 659呎 (2房)
 $1692万
 $25,675/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -41064,7 +41056,7 @@
           <t>B | 523呎 (2房)
 $1337万
 $25,560/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -41072,7 +41064,7 @@
           <t>C | 568呎 (2房)
 $1459万
 $25,688/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41087,7 +41079,7 @@
           <t>A | 659呎 (2房)
 $1675万
 $25,421/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -41095,7 +41087,7 @@
           <t>B | 523呎 (2房)
 $1324万
 $25,307/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -41103,7 +41095,7 @@
           <t>C | 568呎 (2房)
 $1445万
 $25,433/呎
-(24年-06月-13日)</t>
+(24年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -41118,7 +41110,7 @@
           <t>A | 659呎 (2房)
 $1667万
 $25,294/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -41126,7 +41118,7 @@
           <t>B | 523呎 (2房)
 $1317万
 $25,181/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -41134,7 +41126,7 @@
           <t>C | 568呎 (2房)
 $1437万
 $25,307/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -41149,7 +41141,7 @@
           <t>A | 659呎 (2房)
 $1659万
 $25,168/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -41157,7 +41149,7 @@
           <t>B | 523呎 (2房)
 $1310万
 $25,056/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -41165,7 +41157,7 @@
           <t>C | 568呎 (2房)
 $1430万
 $25,181/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -41180,7 +41172,7 @@
           <t>A | 659呎 (2房)
 $1650万
 $25,043/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -41188,7 +41180,7 @@
           <t>B | 523呎 (2房)
 $1304万
 $24,931/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -41196,7 +41188,7 @@
           <t>C | 568呎 (2房)
 $1423万
 $25,056/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -41211,7 +41203,7 @@
           <t>A | 659呎 (2房)
 $1642万
 $24,919/呎
-(24年-08月-05日)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -41219,7 +41211,7 @@
           <t>B | 523呎 (2房)
 $1297万
 $24,807/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -41227,7 +41219,7 @@
           <t>C | 568呎 (2房)
 $1416万
 $24,931/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -41242,15 +41234,15 @@
           <t>A | 659呎 (2房)
 $1634万
 $24,795/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
+(24年-11月-15日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
-$1291万
-$24,684/呎
-(24年-07月-30日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -41258,7 +41250,7 @@
           <t>C | 568呎 (2房)
 $1409万
 $24,807/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41273,7 +41265,7 @@
           <t>A | 656呎 (2房)
 $1618万
 $24,671/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -41281,7 +41273,7 @@
           <t>B | 526呎 (2房)
 $1292万
 $24,561/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -41289,7 +41281,7 @@
           <t>C | 568呎 (2房)
 $1402万
 $24,684/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41296,7 @@
           <t>A | 656呎 (2房)
 $1610万
 $24,549/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -41312,7 +41304,7 @@
           <t>B | 526呎 (2房)
 $1285万
 $24,439/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -41320,7 +41312,7 @@
           <t>C | 568呎 (2房)
 $1395万
 $24,561/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41335,7 +41327,7 @@
           <t>A | 656呎 (2房)
 $1602万
 $24,427/呎
-(24年-05月-12日)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -41343,7 +41335,7 @@
           <t>B | 526呎 (2房)
 $1279万
 $24,317/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -41351,7 +41343,7 @@
           <t>C | 568呎 (2房)
 $1388万
 $24,439/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41366,7 +41358,7 @@
           <t>A | 656呎 (2房)
 $1587万
 $24,185/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -41374,7 +41366,7 @@
           <t>B | 526呎 (2房)
 $1266万
 $24,076/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -41382,7 +41374,7 @@
           <t>C | 568呎 (2房)
 $1374万
 $24,197/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -41397,7 +41389,7 @@
           <t>A | 656呎 (2房)
 $1579万
 $24,064/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -41405,7 +41397,7 @@
           <t>B | 526呎 (2房)
 $1260万
 $23,956/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -41413,7 +41405,7 @@
           <t>C | 568呎 (2房)
 $1368万
 $24,076/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41428,7 +41420,7 @@
           <t>A | 656呎 (2房)
 $1571万
 $23,945/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -41436,7 +41428,7 @@
           <t>B | 526呎 (2房)
 $1254万
 $23,837/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -41444,7 +41436,7 @@
           <t>C | 568呎 (2房)
 $1376万
 $24,223/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41459,7 +41451,7 @@
           <t>A | 656呎 (2房)
 $1563万
 $23,825/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -41467,7 +41459,7 @@
           <t>B | 526呎 (2房)
 $1248万
 $23,719/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -41475,7 +41467,7 @@
           <t>C | 568呎 (2房)
 $1354万
 $23,837/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -41490,7 +41482,7 @@
           <t>A | 656呎 (2房)
 $1555万
 $23,707/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -41498,7 +41490,7 @@
           <t>B | 526呎 (2房)
 $1241万
 $23,601/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -41506,7 +41498,7 @@
           <t>C | 568呎 (2房)
 $1347万
 $23,719/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -41521,7 +41513,7 @@
           <t>A | 656呎 (2房)
 $1547万
 $23,589/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -41529,7 +41521,7 @@
           <t>B | 526呎 (2房)
 $1235万
 $23,483/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -41537,7 +41529,7 @@
           <t>C | 568呎 (2房)
 $1355万
 $23,863/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -41552,7 +41544,7 @@
           <t>A | 656呎 (2房)
 $1429万
 $21,790/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -41560,7 +41552,7 @@
           <t>B | 526呎 (2房)
 $1158万
 $22,014/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -41568,7 +41560,7 @@
           <t>C | 568呎 (2房)
 $1250万
 $22,014/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -41583,7 +41575,7 @@
           <t>A | 656呎 (2房)
 $1361万
 $20,752/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -41591,7 +41583,7 @@
           <t>B | 526呎 (2房)
 $1103万
 $20,966/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -41599,7 +41591,7 @@
           <t>C | 568呎 (2房)
 $1191万
 $20,966/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -41614,7 +41606,7 @@
           <t>A | 656呎 (2房)
 $1335万
 $20,345/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -41622,7 +41614,7 @@
           <t>B | 526呎 (2房)
 $1081万
 $20,555/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -41630,7 +41622,7 @@
           <t>C | 568呎 (2房)
 $1179万
 $20,758/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -41645,7 +41637,7 @@
           <t>A | 656呎 (2房)
 $1331万
 $20,284/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -41653,7 +41645,7 @@
           <t>B | 526呎 (2房)
 $1078万
 $20,493/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -41661,7 +41653,7 @@
           <t>C | 568呎 (2房)
 $1176万
 $20,696/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41668,7 @@
           <t>A | 656呎 (2房)
 $1327万
 $20,223/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -41684,7 +41676,7 @@
           <t>B | 526呎 (2房)
 $1075万
 $20,432/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -41692,7 +41684,7 @@
           <t>C | 568呎 (2房)
 $1172万
 $20,634/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -41707,7 +41699,7 @@
           <t>A | 618呎 (2房)
 $1259万
 $20,371/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -41715,7 +41707,7 @@
           <t>B | 488呎 (2房)
 $1014万
 $20,787/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -41723,7 +41715,7 @@
           <t>C | 530呎 (2房)
 $1166万
 $22,000/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -41858,8 +41850,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr"/>
-      <c r="D5" s="25" t="inlineStr"/>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -41872,7 +41864,7 @@
           <t>A | 903呎 (3房)
 $3070万
 $33,998/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -41880,7 +41872,7 @@
           <t>B | 564呎 (2房)
 $1884万
 $33,400/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -41888,7 +41880,7 @@
           <t>C | 620呎 (2房)
 $1978万
 $31,900/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -41903,7 +41895,7 @@
           <t>A | 903呎 (3房)
 $3043万
 $33,700/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -41911,7 +41903,7 @@
           <t>B | 564呎 (2房)
 $1844万
 $32,700/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -41919,7 +41911,7 @@
           <t>C | 620呎 (2房)
 $1941万
 $31,300/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -41934,7 +41926,7 @@
           <t>A | 900呎 (3房)
 $3043万
 $33,812/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -41942,7 +41934,7 @@
           <t>B | 564呎 (2房)
 $1827万
 $32,400/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -41950,7 +41942,7 @@
           <t>C | 620呎 (2房)
 $1916万
 $30,900/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41957,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -41973,7 +41965,7 @@
           <t>B | 564呎 (2房)
 $1816万
 $32,200/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -41981,7 +41973,7 @@
           <t>C | 620呎 (2房)
 $1904万
 $30,712/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -41996,7 +41988,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,623/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -42004,7 +41996,7 @@
           <t>B | 564呎 (2房)
 $1805万
 $32,000/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -42012,7 +42004,7 @@
           <t>C | 620呎 (2房)
 $1914万
 $30,868/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -42027,7 +42019,7 @@
           <t>A | 903呎 (3房)
 $2899万
 $32,100/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -42035,7 +42027,7 @@
           <t>B | 564呎 (2房)
 $1794万
 $31,800/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -42043,7 +42035,7 @@
           <t>C | 620呎 (2房)
 $1902万
 $30,684/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -42058,7 +42050,7 @@
           <t>A | 903呎 (3房)
 $2935万
 $32,500/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -42066,7 +42058,7 @@
           <t>B | 564呎 (2房)
 $1782万
 $31,600/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -42074,7 +42066,7 @@
           <t>C | 620呎 (2房)
 $1870万
 $30,165/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -42089,7 +42081,7 @@
           <t>A | 903呎 (3房)
 $2862万
 $31,700/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -42097,7 +42089,7 @@
           <t>B | 564呎 (2房)
 $1771万
 $31,400/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -42105,7 +42097,7 @@
           <t>C | 620呎 (2房)
 $1859万
 $29,985/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -42120,7 +42112,7 @@
           <t>A | 903呎 (3房)
 $2872万
 $31,805/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -42128,7 +42120,7 @@
           <t>B | 564呎 (2房)
 $1760万
 $31,200/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -42136,7 +42128,7 @@
           <t>C | 620呎 (2房)
 $1848万
 $29,807/呎
-(24年-06月-16日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -42151,7 +42143,7 @@
           <t>A | 903呎 (3房)
 $2946万
 $32,630/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -42159,7 +42151,7 @@
           <t>B | 564呎 (2房)
 $1779万
 $31,534/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -42167,7 +42159,7 @@
           <t>C | 620呎 (2房)
 $1828万
 $29,482/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -42182,7 +42174,7 @@
           <t>A | 903呎 (3房)
 $3180万
 $35,217/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -42190,7 +42182,7 @@
           <t>B | 564呎 (2房)
 $1687万
 $29,917/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -42198,7 +42190,7 @@
           <t>C | 620呎 (2房)
 $1781万
 $28,732/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42205,7 @@
           <t>A | 903呎 (3房)
 $2781万
 $30,800/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -42221,7 +42213,7 @@
           <t>B | 564呎 (2房)
 $1719万
 $30,482/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -42229,7 +42221,7 @@
           <t>C | 620呎 (2房)
 $1790万
 $28,878/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -42244,7 +42236,7 @@
           <t>A | 903呎 (3房)
 $2798万
 $30,982/呎
-(24年-03月-18日)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -42252,7 +42244,7 @@
           <t>B | 564呎 (2房)
 $1709万
 $30,300/呎
-(24年-08月-13日)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -42260,7 +42252,7 @@
           <t>C | 620呎 (2房)
 $1780万
 $28,706/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42275,7 +42267,7 @@
           <t>A | 903呎 (3房)
 $2745万
 $30,400/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -42283,7 +42275,7 @@
           <t>B | 564呎 (2房)
 $1699万
 $30,119/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -42291,7 +42283,7 @@
           <t>C | 620呎 (2房)
 $1769万
 $28,534/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42306,7 +42298,7 @@
           <t>A | 903呎 (3房)
 $2764万
 $30,604/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -42314,7 +42306,7 @@
           <t>B | 564呎 (2房)
 $1689万
 $29,939/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -42322,7 +42314,7 @@
           <t>C | 620呎 (2房)
 $1759万
 $28,364/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42337,7 +42329,7 @@
           <t>A | 902呎 (3房)
 $2867万
 $31,785/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -42345,7 +42337,7 @@
           <t>B | 567呎 (2房)
 $1725万
 $30,422/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -42353,7 +42345,7 @@
           <t>C | 619呎 (2房)
 $1726万
 $27,885/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42368,7 +42360,7 @@
           <t>A | 902呎 (3房)
 $2697万
 $29,900/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -42376,7 +42368,7 @@
           <t>B | 567呎 (2房)
 $1677万
 $29,583/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -42384,7 +42376,7 @@
           <t>C | 619呎 (2房)
 $1716万
 $27,719/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42391,7 @@
           <t>A | 902呎 (3房)
 $2679万
 $29,700/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -42407,7 +42399,7 @@
           <t>B | 567呎 (2房)
 $1667万
 $29,407/呎
-(24年-08月-19日)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -42415,7 +42407,7 @@
           <t>C | 619呎 (2房)
 $1725万
 $27,860/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42430,7 +42422,7 @@
           <t>A | 902呎 (3房)
 $2661万
 $29,500/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -42438,7 +42430,7 @@
           <t>B | 567呎 (2房)
 $1627万
 $28,693/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -42446,7 +42438,7 @@
           <t>C | 619呎 (2房)
 $1706万
 $27,557/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -42461,7 +42453,7 @@
           <t>A | 902呎 (3房)
 $2634万
 $29,200/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -42469,7 +42461,7 @@
           <t>B | 567呎 (2房)
 $1617万
 $28,522/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -42477,7 +42469,7 @@
           <t>C | 619呎 (2房)
 $1677万
 $27,091/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -42492,7 +42484,7 @@
           <t>A | 902呎 (3房)
 $2713万
 $30,082/呎
-(23年-10月-19日)</t>
+(23年-10月-20日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -42500,7 +42492,7 @@
           <t>B | 567呎 (2房)
 $1590万
 $28,040/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -42508,7 +42500,7 @@
           <t>C | 619呎 (2房)
 $1700万
 $27,468/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -42523,7 +42515,7 @@
           <t>A | 902呎 (3房)
 $2970万
 $32,924/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -42531,7 +42523,7 @@
           <t>B | 567呎 (2房)
 $1598万
 $28,183/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -42539,7 +42531,7 @@
           <t>C | 619呎 (2房)
 $1657万
 $26,769/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42554,7 +42546,7 @@
           <t>A | 902呎 (3房)
 $2589万
 $28,700/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -42562,7 +42554,7 @@
           <t>B | 567呎 (2房)
 $1588万
 $28,014/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -42570,7 +42562,7 @@
           <t>C | 619呎 (2房)
 $1647万
 $26,609/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -42585,7 +42577,7 @@
           <t>A | 902呎 (3房)
 $2571万
 $28,500/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -42593,7 +42585,7 @@
           <t>B | 567呎 (2房)
 $1562万
 $27,541/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -42601,7 +42593,7 @@
           <t>C | 619呎 (2房)
 $1637万
 $26,451/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42616,7 +42608,7 @@
           <t>A | 902呎 (3房)
 $2526万
 $28,000/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -42624,7 +42616,7 @@
           <t>B | 567呎 (2房)
 $1442万
 $25,438/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -42632,7 +42624,7 @@
           <t>C | 619呎 (2房)
 $1530万
 $24,714/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -42647,7 +42639,7 @@
           <t>A | 902呎 (3房)
 $2089万
 $23,156/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -42655,7 +42647,7 @@
           <t>B | 567呎 (2房)
 $1299万
 $22,917/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -42663,7 +42655,7 @@
           <t>C | 619呎 (2房)
 $1391万
 $22,468/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -42678,7 +42670,7 @@
           <t>A | 902呎 (3房)
 $1989万
 $22,053/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -42686,7 +42678,7 @@
           <t>B | 567呎 (2房)
 $1238万
 $21,826/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -42694,7 +42686,7 @@
           <t>C | 619呎 (2房)
 $1337万
 $21,604/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -42709,7 +42701,7 @@
           <t>A | 902呎 (3房)
 $1983万
 $21,987/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -42717,7 +42709,7 @@
           <t>B | 567呎 (2房)
 $1234万
 $21,760/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -42725,7 +42717,7 @@
           <t>C | 619呎 (2房)
 $1333万
 $21,539/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -42740,7 +42732,7 @@
           <t>A | 902呎 (3房)
 $1977万
 $21,921/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -42748,7 +42740,7 @@
           <t>B | 567呎 (2房)
 $1230万
 $21,695/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -42756,7 +42748,7 @@
           <t>C | 619呎 (2房)
 $1329万
 $21,474/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -42771,7 +42763,7 @@
           <t>A | 869呎 (3房)
 $1921万
 $22,106/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -42779,7 +42771,7 @@
           <t>B | 529呎 (2房)
 $1165万
 $22,027/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -42787,7 +42779,7 @@
           <t>C | 597呎 (2房)
 $1292万
 $21,644/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -42922,8 +42914,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr"/>
-      <c r="D5" s="25" t="inlineStr"/>
+      <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -42936,7 +42928,7 @@
           <t>A | 950呎 (3房)
 $3515万
 $37,000/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -42944,7 +42936,7 @@
           <t>B | 781呎 (3房)
 $2761万
 $35,350/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -42952,7 +42944,7 @@
           <t>C | 903呎 (3房)
 $3133万
 $34,700/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -42967,7 +42959,7 @@
           <t>A | 950呎 (3房)
 $3397万
 $35,754/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -42975,7 +42967,7 @@
           <t>B | 781呎 (3房)
 $2706万
 $34,643/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -42983,7 +42975,7 @@
           <t>C | 903呎 (3房)
 $3101万
 $34,340/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42998,7 +42990,7 @@
           <t>A | 950呎 (3房)
 $3473万
 $36,554/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -43006,7 +42998,7 @@
           <t>B | 781呎 (3房)
 $2773万
 $35,510/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -43014,7 +43006,7 @@
           <t>C | 903呎 (3房)
 $3043万
 $33,700/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -43029,7 +43021,7 @@
           <t>A | 950呎 (3房)
 $3914万
 $41,198/呎
-(23年-03月-09日)</t>
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -43037,7 +43029,7 @@
           <t>B | 781呎 (3房)
 $2666万
 $34,138/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -43045,7 +43037,7 @@
           <t>C | 903呎 (3房)
 $3025万
 $33,500/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -43060,7 +43052,7 @@
           <t>A | 950呎 (3房)
 $3539万
 $37,254/呎
-(23年-03月-05日)</t>
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -43068,7 +43060,7 @@
           <t>B | 781呎 (3房)
 $2646万
 $33,880/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -43076,7 +43068,7 @@
           <t>C | 903呎 (3房)
 $3010万
 $33,330/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43091,7 +43083,7 @@
           <t>A | 950呎 (3房)
 $3711万
 $39,061/呎
-(23年-03月-05日)</t>
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -43099,7 +43091,7 @@
           <t>B | 781呎 (3房)
 $2609万
 $33,400/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -43107,7 +43099,7 @@
           <t>C | 903呎 (3房)
 $2989万
 $33,100/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43122,7 +43114,7 @@
           <t>A | 950呎 (3房)
 $3671万
 $38,638/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -43130,7 +43122,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,674/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -43138,7 +43130,7 @@
           <t>C | 903呎 (3房)
 $3340万
 $36,992/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -43153,7 +43145,7 @@
           <t>A | 950呎 (3房)
 $3223万
 $33,928/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -43161,7 +43153,7 @@
           <t>B | 781呎 (3房)
 $2708万
 $34,677/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -43169,7 +43161,7 @@
           <t>C | 903呎 (3房)
 $2953万
 $32,700/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -43184,7 +43176,7 @@
           <t>A | 950呎 (3房)
 $3211万
 $33,800/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -43192,7 +43184,7 @@
           <t>B | 781呎 (3房)
 $2562万
 $32,800/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -43200,7 +43192,7 @@
           <t>C | 903呎 (3房)
 $3046万
 $33,734/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43215,7 +43207,7 @@
           <t>A | 950呎 (3房)
 $3618万
 $38,084/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -43223,7 +43215,7 @@
           <t>B | 781呎 (3房)
 $2530万
 $32,399/呎
-(23年-05月-24日)</t>
+(23年-05月-25日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -43231,7 +43223,7 @@
           <t>C | 903呎 (3房)
 $2888万
 $31,977/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -43246,7 +43238,7 @@
           <t>A | 950呎 (3房)
 $3154万
 $33,200/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -43254,7 +43246,7 @@
           <t>B | 781呎 (3房)
 $2550万
 $32,650/呎
-(23年-03月-13日)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -43262,7 +43254,7 @@
           <t>C | 903呎 (3房)
 $2938万
 $32,538/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -43277,7 +43269,7 @@
           <t>A | 950呎 (3房)
 $3480万
 $36,628/呎
-(22年-12月-12日)</t>
+(22年-12月-13日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -43285,7 +43277,7 @@
           <t>B | 781呎 (3房)
 $2534万
 $32,445/呎
-(23年-03月-06日)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -43293,7 +43285,7 @@
           <t>C | 903呎 (3房)
 $3217万
 $35,626/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -43308,7 +43300,7 @@
           <t>A | 950呎 (3房)
 $3221万
 $33,902/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -43316,7 +43308,7 @@
           <t>B | 781呎 (3房)
 $2491万
 $31,900/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -43324,7 +43316,7 @@
           <t>C | 903呎 (3房)
 $2936万
 $32,514/呎
-(23年-04月-12日)</t>
+(23年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -43339,7 +43331,7 @@
           <t>A | 950呎 (3房)
 $3200万
 $33,687/呎
-(23年-02月-01日)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -43347,7 +43339,7 @@
           <t>B | 781呎 (3房)
 $2476万
 $31,700/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -43355,7 +43347,7 @@
           <t>C | 903呎 (3房)
 $2835万
 $31,400/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -43370,7 +43362,7 @@
           <t>A | 950呎 (3房)
 $3564万
 $37,513/呎
-(23年-01月-12日)</t>
+(23年-01月-13日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -43378,7 +43370,7 @@
           <t>B | 781呎 (3房)
 $2460万
 $31,500/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -43386,7 +43378,7 @@
           <t>C | 903呎 (3房)
 $2817万
 $31,200/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -43401,7 +43393,7 @@
           <t>A | 948呎 (3房)
 $3334万
 $35,165/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -43409,7 +43401,7 @@
           <t>B | 784呎 (3房)
 $2980万
 $38,010/呎
-(22年-12月-27日)</t>
+(22年-12月-28日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -43417,7 +43409,7 @@
           <t>C | 902呎 (3房)
 $2742万
 $30,399/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -43432,7 +43424,7 @@
           <t>A | 948呎 (3房)
 $3268万
 $34,473/呎
-(22年-12月-12日)</t>
+(22年-12月-13日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -43440,7 +43432,7 @@
           <t>B | 784呎 (3房)
 $2465万
 $31,444/呎
-(23年-02月-08日)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -43448,7 +43440,7 @@
           <t>C | 902呎 (3房)
 $3120万
 $34,591/呎
-(23年-02月-08日)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -43463,7 +43455,7 @@
           <t>A | 948呎 (3房)
 $3181万
 $33,555/呎
-(23年-02月-09日)</t>
+(23年-02月-10日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -43471,7 +43463,7 @@
           <t>B | 784呎 (3房)
 $2446万
 $31,200/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -43479,7 +43471,7 @@
           <t>C | 902呎 (3房)
 $3028万
 $33,568/呎
-(23年-02月-27日)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
     </row>
@@ -43494,7 +43486,7 @@
           <t>A | 948呎 (3房)
 $3002万
 $31,667/呎
-(23年-02月-06日)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -43502,7 +43494,7 @@
           <t>B | 784呎 (3房)
 $2447万
 $31,211/呎
-(23年-04月-16日)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -43510,7 +43502,7 @@
           <t>C | 902呎 (3房)
 $2760万
 $30,599/呎
-(22年-12月-21日)</t>
+(22年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -43525,7 +43517,7 @@
           <t>A | 948呎 (3房)
 $2967万
 $31,300/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -43533,7 +43525,7 @@
           <t>B | 784呎 (3房)
 $2564万
 $32,702/呎
-(23年-04月-02日)</t>
+(23年-04月-03日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -43541,7 +43533,7 @@
           <t>C | 902呎 (3房)
 $2756万
 $30,550/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -43556,7 +43548,7 @@
           <t>A | 948呎 (3房)
 $2948万
 $31,100/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -43564,7 +43556,7 @@
           <t>B | 784呎 (3房)
 $2376万
 $30,300/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -43572,7 +43564,7 @@
           <t>C | 902呎 (3房)
 $3070万
 $34,034/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -43587,7 +43579,7 @@
           <t>A | 948呎 (3房)
 $2959万
 $31,209/呎
-(23年-02月-05日)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -43595,7 +43587,7 @@
           <t>B | 784呎 (3房)
 $2670万
 $34,051/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -43603,7 +43595,7 @@
           <t>C | 902呎 (3房)
 $2733万
 $30,300/呎
-(23年-05月-31日)</t>
+(23年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -43618,7 +43610,7 @@
           <t>A | 948呎 (3房)
 $2920万
 $30,800/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -43626,7 +43618,7 @@
           <t>B | 784呎 (3房)
 $2344万
 $29,900/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -43634,7 +43626,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,600/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43641,7 @@
           <t>A | 948呎 (3房)
 $3151万
 $33,235/呎
-(24年-03月-12日)</t>
+(24年-03月-13日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -43657,7 +43649,7 @@
           <t>B | 784呎 (3房)
 $2398万
 $30,590/呎
-(24年-01月-16日)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -43665,7 +43657,7 @@
           <t>C | 902呎 (3房)
 $2670万
 $29,596/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -43680,7 +43672,7 @@
           <t>A | 948呎 (3房)
 $2702万
 $28,500/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -43688,7 +43680,7 @@
           <t>B | 784呎 (3房)
 $2242万
 $28,600/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -43696,7 +43688,7 @@
           <t>C | 902呎 (3房)
 $2598万
 $28,800/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43703,7 @@
           <t>A | 948呎 (3房)
 $2291万
 $24,163/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -43719,7 +43711,7 @@
           <t>B | 784呎 (3房)
 $1850万
 $23,596/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -43727,7 +43719,7 @@
           <t>C | 902呎 (3房)
 $2152万
 $23,856/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -43742,7 +43734,7 @@
           <t>A | 948呎 (3房)
 $2141万
 $22,582/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -43750,7 +43742,7 @@
           <t>B | 784呎 (3房)
 $1745万
 $22,260/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -43758,7 +43750,7 @@
           <t>C | 902呎 (3房)
 $2030万
 $22,506/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43765,7 @@
           <t>A | 948呎 (3房)
 $2130万
 $22,469/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -43781,7 +43773,7 @@
           <t>B | 784呎 (3房)
 $1740万
 $22,194/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -43789,7 +43781,7 @@
           <t>C | 902呎 (3房)
 $2024万
 $22,438/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -43804,7 +43796,7 @@
           <t>A | 948呎 (3房)
 $2119万
 $22,357/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -43812,7 +43804,7 @@
           <t>B | 784呎 (3房)
 $1735万
 $22,127/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -43820,7 +43812,7 @@
           <t>C | 902呎 (3房)
 $2018万
 $22,371/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -43835,7 +43827,7 @@
           <t>A | 915呎 (3房)
 $2060万
 $22,518/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -43843,7 +43835,7 @@
           <t>B | 738呎 (3房)
 $1680万
 $22,764/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -43851,7 +43843,7 @@
           <t>C | 869呎 (3房)
 $1960万
 $22,560/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -43977,10 +43969,10 @@
           <t>A | 2639呎 (4+房)
 $16224万
 $61,476/呎
-(23年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr"/>
+(23年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -43993,7 +43985,7 @@
           <t>A | 1523呎 (3房)
 $6543万
 $42,959/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -44001,7 +43993,7 @@
           <t>B | 1187呎 (3房)
 $4953万
 $41,725/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -44016,7 +44008,7 @@
           <t>A | 1523呎 (3房)
 $5742万
 $37,700/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -44024,7 +44016,7 @@
           <t>B | 1187呎 (3房)
 $4522万
 $38,100/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -44039,7 +44031,7 @@
           <t>A | 1523呎 (3房)
 $5966万
 $39,174/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -44047,7 +44039,7 @@
           <t>B | 1187呎 (3房)
 $5074万
 $42,743/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -44062,7 +44054,7 @@
           <t>A | 1523呎 (3房)
 $5528万
 $36,300/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -44070,7 +44062,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -44085,7 +44077,7 @@
           <t>A | 1523呎 (3房)
 $5498万
 $36,100/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -44093,7 +44085,7 @@
           <t>B | 1187呎 (3房)
 $4439万
 $37,400/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -44108,7 +44100,7 @@
           <t>A | 1523呎 (3房)
 $5969万
 $39,190/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -44116,7 +44108,7 @@
           <t>B | 1187呎 (3房)
 $4380万
 $36,900/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -44131,7 +44123,7 @@
           <t>A | 1523呎 (3房)
 $5986万
 $39,307/呎
-(24年-04月-14日)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -44139,7 +44131,7 @@
           <t>B | 1187呎 (3房)
 $4356万
 $36,700/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -44154,7 +44146,7 @@
           <t>A | 1523呎 (3房)
 $5840万
 $38,346/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -44162,7 +44154,7 @@
           <t>B | 1187呎 (3房)
 $4321万
 $36,400/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -44177,7 +44169,7 @@
           <t>A | 1523呎 (3房)
 $5457万
 $35,830/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -44185,7 +44177,7 @@
           <t>B | 1187呎 (3房)
 $4285万
 $36,100/呎
-(23年-03月-22日)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -44200,7 +44192,7 @@
           <t>A | 1523呎 (3房)
 $5393万
 $35,410/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -44208,7 +44200,7 @@
           <t>B | 1187呎 (3房)
 $4500万
 $37,911/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -44223,7 +44215,7 @@
           <t>A | 1523呎 (3房)
 $5313万
 $34,882/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -44231,7 +44223,7 @@
           <t>B | 1135呎 (3房)
 $4214万
 $37,126/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -44246,7 +44238,7 @@
           <t>A | 1523呎 (3房)
 $5474万
 $35,942/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -44254,7 +44246,7 @@
           <t>B | 1187呎 (3房)
 $4851万
 $40,867/呎
-(23年-03月-19日)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -44269,7 +44261,7 @@
           <t>A | 1523呎 (3房)
 $5387万
 $35,369/呎
-(24年-10月-09日)</t>
+(24年-10月-10日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -44277,7 +44269,7 @@
           <t>B | 1187呎 (3房)
 $4330万
 $36,477/呎
-(23年-02月-21日)</t>
+(23年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -44292,7 +44284,7 @@
           <t>A | 1523呎 (3房)
 $4980万
 $32,700/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -44300,7 +44292,7 @@
           <t>B | 1187呎 (3房)
 $3960万
 $33,361/呎
-(23年-02月-21日)</t>
+(23年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -44315,7 +44307,7 @@
           <t>A | 1523呎 (3房)
 $5364万
 $35,217/呎
-(24年-03月-12日)</t>
+(24年-03月-13日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -44323,7 +44315,7 @@
           <t>B | 1187呎 (3房)
 $4095万
 $34,500/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -44338,7 +44330,7 @@
           <t>A | 1525呎 (3房)
 $4926万
 $32,300/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -44346,7 +44338,7 @@
           <t>B | 1185呎 (3房)
 $4206万
 $35,494/呎
-(23年-05月-16日)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -44361,7 +44353,7 @@
           <t>A | 1525呎 (3房)
 $4956万
 $32,498/呎
-(23年-07月-10日)</t>
+(23年-07月-11日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -44369,7 +44361,7 @@
           <t>B | 1185呎 (3房)
 $4468万
 $37,705/呎
-(22年-12月-07日)</t>
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -44384,7 +44376,7 @@
           <t>A | 1525呎 (3房)
 $5002万
 $32,800/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -44392,7 +44384,7 @@
           <t>B | 1185呎 (3房)
 $4005万
 $33,800/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -44407,7 +44399,7 @@
           <t>A | 1525呎 (3房)
 $5265万
 $34,525/呎
-(23年-02月-14日)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -44415,7 +44407,7 @@
           <t>B | 1185呎 (3房)
 $4092万
 $34,531/呎
-(23年-02月-14日)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -44430,7 +44422,7 @@
           <t>A | 1525呎 (3房)
 $4773万
 $31,300/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -44438,7 +44430,7 @@
           <t>B | 1185呎 (3房)
 $3922万
 $33,100/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -44453,7 +44445,7 @@
           <t>A | 1525呎 (3房)
 $5261万
 $34,497/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -44461,7 +44453,7 @@
           <t>B | 1185呎 (3房)
 $4100万
 $34,599/呎
-(23年-02月-22日)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -44476,7 +44468,7 @@
           <t>A | 1525呎 (3房)
 $5101万
 $33,450/呎
-(22年-12月-11日)</t>
+(22年-12月-12日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -44484,7 +44476,7 @@
           <t>B | 1185呎 (3房)
 $4337万
 $36,596/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -44499,7 +44491,7 @@
           <t>A | 1525呎 (3房)
 $4712万
 $30,900/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -44507,7 +44499,7 @@
           <t>B | 1185呎 (3房)
 $4039万
 $34,084/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -44522,7 +44514,7 @@
           <t>A | 1525呎 (3房)
 $5119万
 $33,566/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -44530,7 +44522,7 @@
           <t>B | 1185呎 (3房)
 $4317万
 $36,433/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -44545,7 +44537,7 @@
           <t>A | 1525呎 (3房)
 $4888万
 $32,050/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -44553,7 +44545,7 @@
           <t>B | 1185呎 (3房)
 $3389万
 $28,600/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -44568,7 +44560,7 @@
           <t>A | 1525呎 (3房)
 $4333万
 $28,410/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -44576,7 +44568,7 @@
           <t>B | 1185呎 (3房)
 $3300万
 $27,848/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -44591,7 +44583,7 @@
           <t>A | 1525呎 (3房)
 $4049万
 $26,552/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -44599,7 +44591,7 @@
           <t>B | 1185呎 (3房)
 $3261万
 $27,522/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -44614,7 +44606,7 @@
           <t>A | 1525呎 (3房)
 $4380万
 $28,720/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -44622,7 +44614,7 @@
           <t>B | 1185呎 (3房)
 $3072万
 $25,920/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -44637,7 +44629,7 @@
           <t>A | 1525呎 (3房)
 $4376万
 $28,692/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -44645,7 +44637,7 @@
           <t>B | 1185呎 (3房)
 $2978万
 $25,131/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -44660,7 +44652,7 @@
           <t>A | 1466呎 (3房)
 $4217万
 $28,768/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -44668,7 +44660,7 @@
           <t>B | 1146呎 (3房)
 $2904万
 $25,336/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -44736,32 +44728,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>6 套</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
@@ -44795,17 +44787,17 @@
           <t>Mansion A</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr"/>
+      <c r="B6" s="30" t="inlineStr"/>
       <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Mansion A (Harbour Light)
 4636呎 (4+房)
-(24年-06月-27日)
+(24年-06月-28日)
 $3.40亿
 $73,339/呎</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr"/>
+      <c r="D6" s="30" t="inlineStr"/>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -44822,8 +44814,8 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr"/>
-      <c r="D7" s="31" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -44831,8 +44823,8 @@
           <t>Mansion C</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr"/>
-      <c r="C8" s="31" t="inlineStr"/>
+      <c r="B8" s="30" t="inlineStr"/>
+      <c r="C8" s="30" t="inlineStr"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Mansion C (Harbour Wave)

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +145,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
@@ -256,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -330,19 +335,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8673,7 +8681,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8681,34 +8689,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H125" s="5" t="n">
+        <v>9163400</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>24699</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>8247060</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22229</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8751,34 +8751,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H126" s="5" t="n">
+        <v>14020000</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>27544</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>12618000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>24790</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -8937,7 +8929,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -8945,34 +8937,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>9145600</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>24651</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>8231040</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>22186</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9007,7 +8991,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9015,34 +8999,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H130" s="5" t="n">
+        <v>13964500</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>27435</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>12568050</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>24692</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
@@ -9201,7 +9177,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9209,34 +9185,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H133" s="5" t="n">
+        <v>9127800</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>24603</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>8215020</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>22143</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9271,7 +9239,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9279,34 +9247,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H134" s="5" t="n">
+        <v>13908900</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>27326</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>12518010</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>24593</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -9481,7 +9441,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9489,34 +9449,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>9108900</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>24552</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>8198010</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>22097</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -9551,7 +9503,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9559,34 +9511,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>13853400</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>27217</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>12468060</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>24495</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
@@ -9745,7 +9689,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9753,34 +9697,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>9091200</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>24505</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>8182080</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22054</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -9815,7 +9751,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -9823,34 +9759,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>13797800</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>27108</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>12418020</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>24397</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -10009,7 +9937,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10017,34 +9945,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H145" s="5" t="n">
+        <v>9072300</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>24454</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>8165070</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>22008</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -10079,7 +9999,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10087,34 +10007,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>13743400</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>27001</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>12369060</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>24301</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -10273,7 +10185,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10281,34 +10193,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H149" s="5" t="n">
+        <v>9054500</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>24406</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>8149050</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>21965</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -10343,7 +10247,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10351,34 +10255,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>13688900</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>26894</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>12320010</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>24204</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -10537,7 +10433,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10545,34 +10441,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H153" s="5" t="n">
+        <v>9036700</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>24358</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>8133030</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>21922</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -10607,7 +10495,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10615,34 +10503,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H154" s="5" t="n">
+        <v>13634500</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>26787</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>12271050</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>24108</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
@@ -10801,7 +10681,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -10809,34 +10689,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>9036700</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>24358</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>8133030</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>21922</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -11057,7 +10929,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11065,34 +10937,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H161" s="5" t="n">
+        <v>9018900</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>24310</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>8117010</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>21879</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -11313,7 +11177,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11321,34 +11185,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H165" s="5" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>24259</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>21833</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -11569,7 +11425,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11577,34 +11433,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>8982300</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>24211</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>8084070</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>21790</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11639,7 +11487,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -11647,34 +11495,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H170" s="5" t="n">
+        <v>13417800</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>26361</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>12076020</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>23725</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -11833,7 +11673,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11841,34 +11681,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>8964500</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>24163</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>8068050</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>21747</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -11903,7 +11735,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11911,34 +11743,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H174" s="5" t="n">
+        <v>13364500</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>26256</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>12028050</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>23631</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -12097,7 +11921,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12105,34 +11929,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>8946700</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>24115</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>8052030</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>21704</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -12167,7 +11983,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12175,34 +11991,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H178" s="5" t="n">
+        <v>13311200</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>26152</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>11980080</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>23537</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12361,7 +12169,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12369,34 +12177,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H181" s="5" t="n">
+        <v>8928900</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>24067</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>8036010</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>21660</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -12431,7 +12231,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -12439,34 +12239,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H182" s="5" t="n">
+        <v>13257800</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>26047</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>11932020</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>23442</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -12625,7 +12417,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12633,34 +12425,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H185" s="5" t="n">
+        <v>8911200</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>24019</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>8020080</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>21617</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -12695,7 +12479,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12703,34 +12487,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H186" s="5" t="n">
+        <v>13205600</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>25944</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>11885040</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>23350</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12889,7 +12665,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12897,34 +12673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>8893400</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>23971</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>8004060</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21574</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -12959,7 +12727,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -12967,34 +12735,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H190" s="5" t="n">
+        <v>13153400</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>25842</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>11838060</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>23257</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13153,7 +12913,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -13161,34 +12921,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H193" s="5" t="n">
+        <v>8893400</v>
+      </c>
+      <c r="I193" s="5" t="n">
+        <v>23971</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K193" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L193" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>8004060</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>21574</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -13223,7 +12975,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -13231,34 +12983,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H194" s="5" t="n">
+        <v>13153400</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>25842</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K194" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L194" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>11838060</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>23257</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N194" s="3" t="inlineStr">
@@ -13417,7 +13161,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13425,34 +13169,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H197" s="5" t="n">
+        <v>8875600</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>23923</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7988040</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>21531</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -13673,7 +13409,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -13681,34 +13417,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H201" s="5" t="n">
+        <v>8857800</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>23875</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>7972020</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>21488</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -13929,7 +13657,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -13937,34 +13665,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H205" s="5" t="n">
+        <v>8840000</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>23827</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>7956000</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21445</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -14193,7 +13913,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14201,34 +13921,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>8822300</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>23780</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7940070</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>21402</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14263,7 +13975,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14271,34 +13983,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H210" s="5" t="n">
+        <v>12893400</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>25331</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>11604060</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>22798</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14457,7 +14161,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14465,34 +14169,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>8804500</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>23732</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>7924050</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>21359</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -14527,7 +14223,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14535,34 +14231,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H214" s="5" t="n">
+        <v>12841200</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>25228</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>11557080</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>22705</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -14721,7 +14409,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -14729,34 +14417,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>8787800</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>23687</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>7909020</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>21318</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
@@ -14791,7 +14471,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14799,34 +14479,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>12790000</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>25128</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>11511000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>22615</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -14985,7 +14657,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14993,34 +14665,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>8516700</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>22956</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7665030</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>20660</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15055,7 +14719,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15063,34 +14727,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>12372300</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>24307</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>11135070</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>21876</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -15125,7 +14781,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15133,34 +14789,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>13315600</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>24035</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>11984040</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>21632</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15257,7 +14905,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15265,34 +14913,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>8516700</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>22956</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>7665030</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>20660</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -15327,7 +14967,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15335,34 +14975,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H226" s="5" t="n">
+        <v>12372300</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>24307</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>11135070</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>21876</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
@@ -15397,7 +15029,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15405,34 +15037,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H227" s="5" t="n">
+        <v>13315600</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>24035</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>11984040</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>21632</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15529,7 +15153,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15537,34 +15161,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H229" s="5" t="n">
+        <v>8418900</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>22692</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>7577010</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>20423</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
@@ -15599,7 +15215,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15607,34 +15223,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H230" s="5" t="n">
+        <v>12205600</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>23980</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>10985040</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>21582</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -15669,7 +15277,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15677,34 +15285,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H231" s="5" t="n">
+        <v>13112300</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>23668</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>11801070</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>21302</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15801,7 +15401,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15809,34 +15409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>8323400</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>22435</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7491060</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>20192</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -15871,7 +15463,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15879,34 +15471,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H234" s="5" t="n">
+        <v>12042300</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>23659</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>10838070</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>21293</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -15941,7 +15525,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -15949,34 +15533,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H235" s="5" t="n">
+        <v>12913400</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>23309</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>11622060</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>20978</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -16073,7 +15649,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16081,34 +15657,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H237" s="5" t="n">
+        <v>8306700</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>22390</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>7476030</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>20151</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
@@ -16143,7 +15711,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16151,34 +15719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H238" s="5" t="n">
+        <v>11994500</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>23565</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>10795050</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>21208</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -16213,7 +15773,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16221,34 +15781,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H239" s="5" t="n">
+        <v>12835600</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>23169</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>11552040</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>20852</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16345,7 +15897,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16353,34 +15905,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H241" s="5" t="n">
+        <v>8290000</v>
+      </c>
+      <c r="I241" s="5" t="n">
+        <v>22345</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L241" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>7461000</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>20111</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16415,7 +15959,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16423,34 +15967,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H242" s="5" t="n">
+        <v>11946700</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>23471</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>10752030</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>21124</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -16485,7 +16021,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16493,34 +16029,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H243" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I243" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H243" s="5" t="n">
+        <v>12878900</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>23247</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K243" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L243" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>11591010</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>20922</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>180天付款計劃</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
@@ -39414,22 +38942,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -39507,20 +39035,20 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+$1402万
+$27,544/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$916万
+$24,699/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39546,20 +39074,20 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
+$1396万
+$27,435/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$915万
+$24,651/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39585,20 +39113,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$1391万
+$27,326/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$913万
+$24,603/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39624,20 +39152,20 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$1385万
+$27,217/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$911万
+$24,552/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39663,20 +39191,20 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$1380万
+$27,108/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$909万
+$24,505/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39702,20 +39230,20 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+$1374万
+$27,001/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$907万
+$24,454/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39741,20 +39269,20 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$1369万
+$26,894/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$905万
+$24,406/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39780,20 +39308,20 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$1363万
+$26,787/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$904万
+$24,358/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39827,12 +39355,12 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$904万
+$24,358/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39866,12 +39394,12 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$902万
+$24,310/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39905,12 +39433,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$900万
+$24,259/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39936,20 +39464,20 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$1342万
+$26,361/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$898万
+$24,211/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39975,20 +39503,20 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$1336万
+$26,256/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$896万
+$24,163/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40014,20 +39542,20 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$1331万
+$26,152/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$895万
+$24,115/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40053,20 +39581,20 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$1326万
+$26,047/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$893万
+$24,067/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40092,20 +39620,20 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$1321万
+$25,944/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$891万
+$24,019/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40131,20 +39659,20 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$1315万
+$25,842/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$889万
+$23,971/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40170,20 +39698,20 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$1315万
+$25,842/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$889万
+$23,971/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40217,12 +39745,12 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$888万
+$23,923/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40256,12 +39784,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$886万
+$23,875/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40295,12 +39823,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$884万
+$23,827/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40326,20 +39854,20 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+$1289万
+$25,331/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$882万
+$23,780/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40365,20 +39893,20 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+$1284万
+$25,228/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$880万
+$23,732/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40404,20 +39932,20 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+$1279万
+$25,128/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$879万
+$23,687/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40435,28 +39963,28 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
+$1332万
+$24,035/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+$1237万
+$24,307/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$852万
+$22,956/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40474,28 +40002,28 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
+$1332万
+$24,035/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+$1237万
+$24,307/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$852万
+$22,956/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40513,28 +40041,28 @@
 (25年-08月-27日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
+$1311万
+$23,668/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+$1221万
+$23,980/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$842万
+$22,692/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40552,28 +40080,28 @@
 (25年-09月-01日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
+$1291万
+$23,309/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
+$1204万
+$23,659/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$832万
+$22,435/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40591,28 +40119,28 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
+$1284万
+$23,169/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+$1199万
+$23,565/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$831万
+$22,390/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40630,28 +40158,28 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
+$1288万
+$23,247/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
+$1195万
+$23,471/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
--
--
-(待售)</t>
+$829万
+$22,345/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -44728,32 +44256,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>6 套</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
@@ -44787,7 +44315,7 @@
           <t>Mansion A</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr"/>
+      <c r="B6" s="31" t="inlineStr"/>
       <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Mansion A (Harbour Light)
@@ -44797,7 +44325,7 @@
 $73,339/呎</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -44814,8 +44342,8 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr"/>
-      <c r="D7" s="30" t="inlineStr"/>
+      <c r="C7" s="31" t="inlineStr"/>
+      <c r="D7" s="31" t="inlineStr"/>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -44823,8 +44351,8 @@
           <t>Mansion C</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr"/>
-      <c r="C8" s="30" t="inlineStr"/>
+      <c r="B8" s="31" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Mansion C (Harbour Wave)

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -18881,38 +18881,30 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>14644000</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>28000</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K289" s="5" t="n">
+        <v>14644000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>28000</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -18921,7 +18913,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40254,7 +40246,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40264,7 +40256,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40765,12 +40757,12 @@
 (24年-11月-15日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 523呎 (2房)
-招标单位
--
-(在售)</t>
+$1464万
+$28,000/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -1863,38 +1863,30 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>113302860</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>54264</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K18" s="5" t="n">
+        <v>113302860</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>54264</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2425,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1870</v>
+        <v>1816</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2442,14 +2434,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
         <v>92783000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>49617</v>
+        <v>51092</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2460,7 +2452,7 @@
         <v>92783000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>49617</v>
+        <v>51092</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -5365,7 +5357,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1870</v>
+        <v>1816</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5374,14 +5366,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
         <v>91462500</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>48910</v>
+        <v>50365</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5392,7 +5384,7 @@
         <v>91462500</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>48910</v>
+        <v>50365</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5427,7 +5419,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1909</v>
+        <v>1855</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5436,14 +5428,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
         <v>97037500</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>50832</v>
+        <v>52311</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5454,7 +5446,7 @@
         <v>97037500</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>50832</v>
+        <v>52311</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -9301,38 +9293,30 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>14514800</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>26200</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K135" s="5" t="n">
+        <v>14514800</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>26200</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9689,7 +9673,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9751,7 +9735,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10305,7 +10289,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10314,14 +10298,14 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
         <v>13351400</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>24100</v>
+        <v>24144</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10332,7 +10316,7 @@
         <v>13351400</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>24100</v>
+        <v>24144</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10929,7 +10913,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11177,7 +11161,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11425,7 +11409,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11487,7 +11471,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -12537,7 +12521,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12553,7 +12537,7 @@
         <v>12797400</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>23100</v>
+        <v>23142</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -12564,7 +12548,7 @@
         <v>12797400</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>23100</v>
+        <v>23142</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -13161,7 +13145,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13409,7 +13393,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -13657,23 +13641,23 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>8840000</v>
+        <v>7956000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>23827</v>
+        <v>21445</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
@@ -13684,7 +13668,7 @@
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -14161,7 +14145,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14223,7 +14207,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14281,7 +14265,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -14290,14 +14274,14 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
         <v>12465000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>22500</v>
+        <v>22541</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -14308,7 +14292,7 @@
         <v>12465000</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>22500</v>
+        <v>22541</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -14657,7 +14641,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14719,7 +14703,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -14781,7 +14765,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -14905,7 +14889,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -14967,7 +14951,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15029,7 +15013,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15649,7 +15633,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -15711,7 +15695,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -15773,7 +15757,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16145,38 +16129,30 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>43080000</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>38846</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L245" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K245" s="5" t="n">
+        <v>43080000</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>38846</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -16185,7 +16161,7 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37325,7 +37301,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -37335,7 +37311,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37533,12 +37509,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 2088呎 (4+房)
-招标单位
--
-(在售)</t>
+$11330万
+$54,264/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -37658,10 +37634,10 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
+          <t>B | 1816呎 (4+房)
 $9278万
-$49,617/呎
-(26年-07月-04日)</t>
+$51,092/呎
+(26年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -38290,18 +38266,18 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
+          <t>A | 1855呎 (4+房)
 $9704万
-$50,832/呎
-(26年-07月-07日)</t>
+$52,311/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
+          <t>B | 1816呎 (4+房)
 $9146万
-$48,910/呎
-(26年-07月-07日)</t>
+$50,365/呎
+(26年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -38929,27 +38905,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
@@ -39097,12 +39073,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
--
--
-(待售)</t>
+$1451万
+$26,200/呎
+(26年-08月-09日)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -39183,20 +39159,20 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1380万
 $27,108/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $909万
 $24,505/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39255,10 +39231,10 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1335万
-$24,100/呎
-(26年-07月-17日)</t>
+$24,144/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -39386,12 +39362,12 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $902万
 $24,310/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39425,12 +39401,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $900万
 $24,259/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39456,20 +39432,20 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1342万
 $26,361/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $898万
 $24,211/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39606,9 +39582,9 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1280万
-$23,100/呎
+$23,142/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -39737,12 +39713,12 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $888万
 $23,923/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39776,12 +39752,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $886万
 $23,875/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39815,12 +39791,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
-$884万
-$23,827/呎
-(已定价未售)</t>
+$796万
+$21,445/呎
+(26年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -39879,26 +39855,26 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1246万
-$22,500/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
+$22,541/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1284万
 $25,228/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $880万
 $23,732/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39955,28 +39931,28 @@
 (25年-08月-13日)</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1332万
 $24,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1237万
 $24,307/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $852万
 $22,956/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39994,28 +39970,28 @@
 (25年-08月-28日)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1332万
 $24,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1237万
 $24,307/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $852万
 $22,956/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40111,28 +40087,28 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1284万
 $23,169/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1199万
 $23,565/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $831万
 $22,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40246,7 +40222,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40256,7 +40232,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40298,12 +40274,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 1109呎 (3房)
-招标单位
--
-(在售)</t>
+$4308万
+$38,846/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37246,23 +37246,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>1座 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>沄璟 - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -37293,748 +37294,117 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>36&amp;37</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 3442呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 3138呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$12605万
-$60,370/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>A | 2034呎 (4+房)
-$12522万
-$61,562/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$12446万
-$59,609/呎
-(24年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$11330万
-$54,264/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$9230万
-$49,358/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$11761万
-$56,327/呎
-(25年-12月-23日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$9483万
-$50,710/呎
-(25年-12月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$12055万
-$57,737/呎
-(23年-03月-15日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8796万
-$47,036/呎
-(23年-03月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$11467万
-$54,916/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$9233万
-$49,376/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10557万
-$50,561/呎
-(23年-02月-08日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$12038万
-$57,653/呎
-(24年-04月-18日)</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>B | 1816呎 (4+房)
-$9278万
-$51,092/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10255万
-$49,113/呎
-(23年-02月-03日)</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8013万
-$42,850/呎
-(24年-04月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10110万
-$48,419/呎
-(23年-01月-31日)</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>B | 1816呎 (4+房)
-$9054万
-$49,856/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10252万
-$49,100/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8578万
-$45,870/呎
-(25年-10月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10085万
-$48,300/呎
-(24年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8929万
-$47,748/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$10117万
-$48,453/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>B | 1816呎 (4+房)
-$8690万
-$47,852/呎
-(26年-07月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9855万
-$47,200/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8308万
-$44,429/呎
-(26年-03月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9587万
-$45,913/呎
-(23年-02月-15日)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8207万
-$43,889/呎
-(25年-12月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9324万
-$44,653/呎
-(23年-01月-31日)</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8477万
-$45,333/呎
-(25年-10月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9542万
-$45,700/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7386万
-$39,500/呎
-(24年-06月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9420万
-$45,115/呎
-(23年-01月-20日)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7939万
-$42,457/呎
-(25年-10月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$8403万
-$40,242/呎
-(23年-01月-13日)</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7315万
-$39,120/呎
-(23年-01月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$8456万
-$40,500/呎
-(23年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7143万
-$38,200/呎
-(23年-03月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9271万
-$44,400/呎
-(25年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8182万
-$43,753/呎
-(25年-10月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9703万
-$46,472/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7750万
-$41,444/呎
-(24年-04月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9127万
-$43,710/呎
-(23年-03月-15日)</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7696万
-$41,157/呎
-(26年-01月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$9427万
-$45,150/呎
-(24年-04月-18日)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$7684万
-$41,089/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-$8658万
-$43,617/呎
-(24年-11月-06日)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>B | 1797呎 (4+房)
-$7178万
-$39,946/呎
-(24年-11月-06日)</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>6 套</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/屋号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Breeze</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Light</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Harbour Wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mansion A</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr"/>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Mansion A (Harbour Light)
+4636呎 (4+房)
+(24年-06月-28日)
+$3.40亿
+$73,339/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr"/>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Mansion B</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Mansion B (Harbour Breeze)
+4294呎 (4+房)
+(暂停销售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr"/>
+      <c r="D7" s="31" t="inlineStr"/>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Mansion C</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Mansion C (Harbour Wave)
+4850呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -38058,7 +37428,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -38102,7 +37472,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38112,12 +37482,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -38151,18 +37521,18 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3406呎 (4+房)
+          <t>A | 3442呎 (4+房)
 -
 -
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>B | 3137呎 (4+房)
-招标单位
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 3138呎 (4+房)
 -
-(在售)</t>
+-
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -38174,7 +37544,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
+          <t>A | 2088呎 (4+房)
 -
 -
 (待售)</t>
@@ -38197,7 +37567,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
+          <t>A | 2088呎 (4+房)
 -
 -
 (待售)</t>
@@ -38220,7 +37590,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
+          <t>A | 2088呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -38241,12 +37611,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-招标单位
--
-(在售)</t>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12605万
+$60,370/呎
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38266,36 +37636,13 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 1855呎 (4+房)
-$9704万
-$52,311/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>B | 1816呎 (4+房)
-$9146万
-$50,365/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+          <t>A | 2034呎 (4+房)
+$12522万
+$61,562/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38304,67 +37651,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-$8415万
-$45,000/呎
-(24年-04月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-$9434万
-$49,421/呎
-(24年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12446万
+$59,609/呎
+(24年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38373,6 +37674,75 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$11330万
+$54,264/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9230万
+$49,358/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$11761万
+$56,327/呎
+(25年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9483万
+$50,710/呎
+(25年-12月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$12055万
+$57,737/呎
+(23年-03月-15日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8796万
+$47,036/呎
+(23年-03月-15日)</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -38381,13 +37751,36 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$9490万
-$49,712/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+          <t>A | 2088呎 (4+房)
+$11467万
+$54,916/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$9233万
+$49,376/呎
+(26年-02月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$10557万
+$50,561/呎
+(23年-02月-08日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
 招标单位
@@ -38396,29 +37789,6 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>A | 1909呎 (4+房)
-$8880万
-$46,517/呎
-(23年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
@@ -38427,18 +37797,18 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$9295万
-$48,690/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
+          <t>A | 2088呎 (4+房)
+$12038万
+$57,653/呎
+(24年-04月-18日)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9278万
+$51,092/呎
+(26年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -38450,18 +37820,18 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$9015万
-$47,221/呎
-(23年-07月-06日)</t>
+          <t>A | 2088呎 (4+房)
+$10255万
+$49,113/呎
+(23年-02月-03日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 1816呎 (4+房)
-$9086万
-$50,033/呎
-(26年-07月-07日)</t>
+          <t>B | 1870呎 (4+房)
+$8013万
+$42,850/呎
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -38473,18 +37843,18 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$9017万
-$47,236/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
+          <t>A | 2088呎 (4+房)
+$10110万
+$48,419/呎
+(23年-01月-31日)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9054万
+$49,856/呎
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -38496,18 +37866,18 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8552万
-$44,800/呎
-(25年-02月-17日)</t>
+          <t>A | 2088呎 (4+房)
+$10252万
+$49,100/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$8265万
-$44,200/呎
-(25年-02月-17日)</t>
+$8578万
+$45,870/呎
+(25年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -38519,18 +37889,18 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8837万
-$46,290/呎
-(25年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
+          <t>A | 2088呎 (4+房)
+$10085万
+$48,300/呎
+(24年-11月-25日)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-招标单位
--
-(在售)</t>
+$8929万
+$47,748/呎
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -38542,18 +37912,18 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8302万
-$43,490/呎
-(24年-09月-11日)</t>
+          <t>A | 2088呎 (4+房)
+$10117万
+$48,453/呎
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
-$8103万
-$43,329/呎
-(24年-09月-11日)</t>
+          <t>B | 1816呎 (4+房)
+$8690万
+$47,852/呎
+(26年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -38565,18 +37935,18 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7865万
-$41,200/呎
-(24年-08月-07日)</t>
+          <t>A | 2088呎 (4+房)
+$9855万
+$47,200/呎
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7667万
-$41,000/呎
-(24年-08月-07日)</t>
+$8308万
+$44,429/呎
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -38588,18 +37958,18 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7770万
-$40,700/呎
-(24年-08月-07日)</t>
+          <t>A | 2088呎 (4+房)
+$9587万
+$45,913/呎
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7574万
-$40,500/呎
-(24年-08月-07日)</t>
+$8207万
+$43,889/呎
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -38611,18 +37981,18 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8062万
-$42,231/呎
-(24年-07月-22日)</t>
+          <t>A | 2088呎 (4+房)
+$9324万
+$44,653/呎
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$8054万
-$43,070/呎
-(25年-03月-11日)</t>
+$8477万
+$45,333/呎
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -38634,18 +38004,18 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8319万
-$43,579/呎
-(24年-05月-23日)</t>
+          <t>A | 2088呎 (4+房)
+$9542万
+$45,700/呎
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7630万
-$40,800/呎
-(25年-03月-11日)</t>
+$7386万
+$39,500/呎
+(24年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -38657,18 +38027,18 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7882万
-$41,290/呎
-(24年-05月-16日)</t>
+          <t>A | 2088呎 (4+房)
+$9420万
+$45,115/呎
+(23年-01月-20日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7904万
-$42,270/呎
-(25年-03月-04日)</t>
+$7939万
+$42,457/呎
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -38680,18 +38050,18 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7470万
-$39,130/呎
-(23年-07月-06日)</t>
+          <t>A | 2088呎 (4+房)
+$8403万
+$40,242/呎
+(23年-01月-13日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7860万
-$42,029/呎
-(25年-03月-11日)</t>
+$7315万
+$39,120/呎
+(23年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -38703,18 +38073,18 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8131万
-$42,595/呎
-(25年-11月-10日)</t>
+          <t>A | 2088呎 (4+房)
+$8456万
+$40,500/呎
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7800万
-$41,710/呎
-(26年-02月-27日)</t>
+$7143万
+$38,200/呎
+(23年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -38726,18 +38096,18 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$8104万
-$42,453/呎
-(25年-11月-10日)</t>
+          <t>A | 2088呎 (4+房)
+$9271万
+$44,400/呎
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$8167万
-$43,673/呎
-(25年-12月-08日)</t>
+$8182万
+$43,753/呎
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -38749,18 +38119,18 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7708万
-$40,377/呎
-(24年-05月-17日)</t>
+          <t>A | 2088呎 (4+房)
+$9703万
+$46,472/呎
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7532万
-$40,276/呎
-(24年-05月-20日)</t>
+$7750万
+$41,444/呎
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -38772,18 +38142,18 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7292万
-$38,200/呎
-(24年-06月-20日)</t>
+          <t>A | 2088呎 (4+房)
+$9127万
+$43,710/呎
+(23年-03月-15日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 1870呎 (4+房)
-$7704万
-$41,196/呎
-(25年-08月-14日)</t>
+$7696万
+$41,157/呎
+(26年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -38795,18 +38165,18 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 1909呎 (4+房)
-$7576万
-$39,687/呎
-(24年-11月-11日)</t>
+          <t>A | 2088呎 (4+房)
+$9427万
+$45,150/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>B | 1816呎 (4+房)
-$7996万
-$44,028/呎
-(26年-05月-12日)</t>
+          <t>B | 1870呎 (4+房)
+$7684万
+$41,089/呎
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -38818,18 +38188,18 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 1828呎 (4+房)
-$7534万
-$41,213/呎
-(25年-11月-11日)</t>
+          <t>A | 1985呎 (4+房)
+$8658万
+$43,617/呎
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 1797呎 (4+房)
-$7380万
-$41,069/呎
-(26年-03月-24日)</t>
+$7178万
+$39,946/呎
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -38848,20 +38218,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3A座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -38900,32 +38268,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -38945,1209 +38313,694 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>A | 1129呎 (3房)
-$5215万
-$46,195/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>B | 1334呎 (3房)
-$3869万
-$29,000/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr"/>
-      <c r="E5" s="24" t="inlineStr"/>
+          <t>36&amp;37</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3406呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 3137呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1546万
-$26,800/呎
-(25年-08月-26日)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1391万
-$25,145/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1402万
-$27,544/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$916万
-$24,699/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1512万
-$26,200/呎
-(25年-08月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1363万
-$24,644/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1396万
-$27,435/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$915万
-$24,651/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1451万
-$26,200/呎
-(26年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1391万
-$27,326/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$913万
-$24,603/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1489万
-$25,810/呎
-(25年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1324万
-$23,900/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1385万
-$27,217/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$911万
-$24,552/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1482万
-$25,681/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1319万
-$23,843/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1380万
-$27,108/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$909万
-$24,505/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1474万
-$25,554/呎
-(25年-08月-15日)</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1341万
-$24,244/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1374万
-$27,001/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$907万
-$24,454/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1467万
-$25,426/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1335万
-$24,144/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1369万
-$26,894/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$905万
-$24,406/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1460万
-$25,300/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1319万
-$23,800/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1363万
-$26,787/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$904万
-$24,358/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1469万
-$25,454/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1285万
-$23,200/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1196万
-$23,500/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$904万
-$24,358/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1438万
-$24,925/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1274万
-$23,000/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1191万
-$23,400/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$902万
-$24,310/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1431万
-$24,801/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1269万
-$22,900/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1186万
-$23,300/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$900万
-$24,259/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1424万
-$24,677/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1302万
-$23,542/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1342万
-$26,361/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$898万
-$24,211/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1417万
-$24,555/呎
-(25年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1280万
-$23,100/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1336万
-$26,256/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$896万
-$24,163/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1410万
-$24,432/呎
-(24年-11月-15日)</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1274万
-$23,042/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1331万
-$26,152/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$895万
-$24,115/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1403万
-$24,311/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1285万
-$23,242/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1326万
-$26,047/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$893万
-$24,067/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1411万
-$24,459/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1280万
-$23,142/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1321万
-$25,944/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$891万
-$24,019/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1389万
-$24,070/呎
-(24年-12月-04日)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1274万
-$23,042/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1315万
-$25,842/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$889万
-$23,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1382万
-$23,950/呎
-(24年-12月-31日)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1274万
-$23,042/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1315万
-$25,842/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$889万
-$23,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1368万
-$23,713/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1258万
-$22,700/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1155万
-$22,700/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$888万
-$23,923/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1361万
-$23,595/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1252万
-$22,641/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1150万
-$22,600/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$886万
-$23,875/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1355万
-$23,477/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1295万
-$23,377/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$796万
-$21,445/呎
-(26年-08月-09日)</t>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1855呎 (4+房)
+$9704万
+$52,311/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9146万
+$50,365/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8415万
+$45,000/呎
+(24年-04月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9434万
+$49,421/呎
+(24年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9490万
+$49,712/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8880万
+$46,517/呎
+(23年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9295万
+$48,690/呎
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9015万
+$47,221/呎
+(23年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$9086万
+$50,033/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$9017万
+$47,236/呎
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8552万
+$44,800/呎
+(25年-02月-17日)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8265万
+$44,200/呎
+(25年-02月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8837万
+$46,290/呎
+(25年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8302万
+$43,490/呎
+(24年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8103万
+$43,329/呎
+(24年-09月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7865万
+$41,200/呎
+(24年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7667万
+$41,000/呎
+(24年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$7770万
+$40,700/呎
+(24年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7574万
+$40,500/呎
+(24年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8062万
+$42,231/呎
+(24年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8054万
+$43,070/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 1909呎 (4+房)
+$8319万
+$43,579/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7630万
+$40,800/呎
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1348万
-$23,361/呎
-(25年-08月-13日)</t>
+          <t>A | 1909呎 (4+房)
+$7882万
+$41,290/呎
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 553呎 (2房)
-$1252万
-$22,641/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1289万
-$25,331/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$882万
-$23,780/呎
-(已定价未售)</t>
+          <t>B | 1870呎 (4+房)
+$7904万
+$42,270/呎
+(25年-03月-04日)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1341万
-$23,244/呎
-(25年-08月-11日)</t>
+          <t>A | 1909呎 (4+房)
+$7470万
+$39,130/呎
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 553呎 (2房)
-$1246万
-$22,541/呎
-(26年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1284万
-$25,228/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$880万
-$23,732/呎
-(在售)</t>
+          <t>B | 1870呎 (4+房)
+$7860万
+$42,029/呎
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1335万
-$23,129/呎
-(25年-08月-12日)</t>
+          <t>A | 1909呎 (4+房)
+$8131万
+$42,595/呎
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
-$1235万
-$22,300/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1279万
-$25,128/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$879万
-$23,687/呎
-(已定价未售)</t>
+          <t>B | 1870呎 (4+房)
+$7800万
+$41,710/呎
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1247万
-$21,606/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1332万
-$24,035/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1237万
-$24,307/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$852万
-$22,956/呎
-(在售)</t>
+          <t>A | 1909呎 (4+房)
+$8104万
+$42,453/呎
+(25年-11月-10日)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$8167万
+$43,673/呎
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1210万
-$20,976/呎
-(25年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1332万
-$24,035/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1237万
-$24,307/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$852万
-$22,956/呎
-(在售)</t>
+          <t>A | 1909呎 (4+房)
+$7708万
+$40,377/呎
+(24年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7532万
+$40,276/呎
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1198万
-$20,769/呎
-(25年-08月-27日)</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1311万
-$23,668/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1221万
-$23,980/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$842万
-$22,692/呎
-(已定价未售)</t>
+          <t>A | 1909呎 (4+房)
+$7292万
+$38,200/呎
+(24年-06月-20日)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 1870呎 (4+房)
+$7704万
+$41,196/呎
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1195万
-$20,706/呎
-(25年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1291万
-$23,309/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1204万
-$23,659/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$832万
-$22,435/呎
-(已定价未售)</t>
+          <t>A | 1909呎 (4+房)
+$7576万
+$39,687/呎
+(24年-11月-11日)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 1816呎 (4+房)
+$7996万
+$44,028/呎
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 577呎 (2房)
-$1191万
-$20,644/呎
-(25年-09月-22日)</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1284万
-$23,169/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1199万
-$23,565/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$831万
-$22,390/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>A | 539呎 (2房)
-$1197万
-$22,200/呎
-(25年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>B | 554呎 (2房)
-$1288万
-$23,247/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1195万
-$23,471/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$829万
-$22,345/呎
-(已定价未售)</t>
+          <t>A | 1828呎 (4+房)
+$7534万
+$41,213/呎
+(25年-11月-11日)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 1797呎 (4+房)
+$7380万
+$41,069/呎
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -40173,12 +39026,13 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3B座 销控网格图</t>
+          <t>3A座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -40217,32 +39071,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -40267,6 +39121,11 @@
           <t>C</t>
         </is>
       </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -40276,14 +39135,22 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>A | 1109呎 (3房)
-$4308万
-$38,846/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr"/>
+          <t>A | 1129呎 (3房)
+$5215万
+$46,195/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>B | 1334呎 (3房)
+$3869万
+$29,000/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
       <c r="D5" s="24" t="inlineStr"/>
+      <c r="E5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -40293,26 +39160,34 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1799万
-$27,300/呎
-(25年-08月-22日)</t>
+          <t>A | 577呎 (2房)
+$1546万
+$26,800/呎
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1423万
-$27,200/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1551万
-$27,300/呎
-(25年-08月-08日)</t>
+          <t>B | 553呎 (2房)
+$1391万
+$25,145/呎
+(26年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1402万
+$27,544/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$916万
+$24,699/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40324,26 +39199,34 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1766万
-$26,800/呎
-(25年-08月-08日)</t>
+          <t>A | 577呎 (2房)
+$1512万
+$26,200/呎
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
+          <t>B | 553呎 (2房)
+$1363万
+$24,644/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
 $1396万
-$26,700/呎
-(25年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1522万
-$26,800/呎
-(25年-08月-13日)</t>
+$27,435/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$915万
+$24,651/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40353,28 +39236,36 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>A | 659呎 (2房)
-$1746万
-$26,500/呎
-(25年-09月-01日)</t>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1381万
-$26,400/呎
-(25年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1505万
-$26,500/呎
-(25年-08月-28日)</t>
+          <t>B | 554呎 (2房)
+$1451万
+$26,200/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1391万
+$27,326/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$913万
+$24,603/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40386,26 +39277,34 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1735万
-$26,323/呎
-(25年-03月-12日)</t>
+          <t>A | 577呎 (2房)
+$1489万
+$25,810/呎
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1371万
-$26,205/呎
-(24年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>C | 1644呎 (2房)
-$1496万
-$9,099/呎
-(24年-06月-17日)</t>
+          <t>B | 554呎 (2房)
+$1324万
+$23,900/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1385万
+$27,217/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$911万
+$24,552/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40417,26 +39316,34 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1726万
-$26,192/呎
-(25年-06月-17日)</t>
+          <t>A | 577呎 (2房)
+$1482万
+$25,681/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1364万
-$26,075/呎
-(25年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1488万
-$26,205/呎
-(24年-05月-10日)</t>
+          <t>B | 553呎 (2房)
+$1319万
+$23,843/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1380万
+$27,108/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$909万
+$24,505/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40448,26 +39355,34 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1717万
-$26,062/呎
-(24年-04月-30日)</t>
+          <t>A | 577呎 (2房)
+$1474万
+$25,554/呎
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1357万
-$25,945/呎
-(25年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1481万
-$26,075/呎
-(24年-04月-30日)</t>
+          <t>B | 553呎 (2房)
+$1341万
+$24,244/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1374万
+$27,001/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$907万
+$24,454/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40479,26 +39394,34 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1709万
-$25,932/呎
-(25年-06月-03日)</t>
+          <t>A | 577呎 (2房)
+$1467万
+$25,426/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1350万
-$25,816/呎
-(24年-05月-23日)</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1474万
-$25,945/呎
-(24年-04月-24日)</t>
+          <t>B | 553呎 (2房)
+$1335万
+$24,144/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1369万
+$26,894/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$905万
+$24,406/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40510,26 +39433,34 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1700万
-$25,803/呎
-(25年-04月-29日)</t>
+          <t>A | 577呎 (2房)
+$1460万
+$25,300/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1343万
-$25,688/呎
-(24年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1466万
-$25,816/呎
-(24年-04月-30日)</t>
+          <t>B | 554呎 (2房)
+$1319万
+$23,800/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1363万
+$26,787/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$904万
+$24,358/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40541,26 +39472,34 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1692万
-$25,675/呎
-(24年-11月-25日)</t>
+          <t>A | 577呎 (2房)
+$1469万
+$25,454/呎
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1337万
-$25,560/呎
-(24年-11月-19日)</t>
+          <t>B | 554呎 (2房)
+$1285万
+$23,200/呎
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 568呎 (2房)
-$1459万
-$25,688/呎
-(24年-05月-23日)</t>
+          <t>C | 509呎 (2房)
+$1196万
+$23,500/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$904万
+$24,358/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40572,26 +39511,34 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1675万
-$25,421/呎
-(25年-02月-28日)</t>
+          <t>A | 577呎 (2房)
+$1438万
+$24,925/呎
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1324万
-$25,307/呎
-(25年-08月-14日)</t>
+          <t>B | 554呎 (2房)
+$1274万
+$23,000/呎
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 568呎 (2房)
-$1445万
-$25,433/呎
-(24年-06月-14日)</t>
+          <t>C | 509呎 (2房)
+$1191万
+$23,400/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$902万
+$24,310/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40603,26 +39550,34 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1667万
-$25,294/呎
-(24年-06月-07日)</t>
+          <t>A | 577呎 (2房)
+$1431万
+$24,801/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1317万
-$25,181/呎
-(24年-05月-09日)</t>
+          <t>B | 554呎 (2房)
+$1269万
+$22,900/呎
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 568呎 (2房)
-$1437万
-$25,307/呎
-(25年-10月-16日)</t>
+          <t>C | 509呎 (2房)
+$1186万
+$23,300/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$900万
+$24,259/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40634,26 +39589,34 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1659万
-$25,168/呎
-(24年-11月-18日)</t>
+          <t>A | 577呎 (2房)
+$1424万
+$24,677/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1310万
-$25,056/呎
-(24年-09月-17日)</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1430万
-$25,181/呎
-(24年-04月-30日)</t>
+          <t>B | 553呎 (2房)
+$1302万
+$23,542/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1342万
+$26,361/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$898万
+$24,211/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40665,26 +39628,34 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1650万
-$25,043/呎
-(24年-05月-16日)</t>
+          <t>A | 577呎 (2房)
+$1417万
+$24,555/呎
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1304万
-$24,931/呎
-(24年-09月-17日)</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1423万
-$25,056/呎
-(24年-04月-15日)</t>
+          <t>B | 554呎 (2房)
+$1280万
+$23,100/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1336万
+$26,256/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$896万
+$24,163/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40696,26 +39667,34 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1642万
-$24,919/呎
-(24年-08月-06日)</t>
+          <t>A | 577呎 (2房)
+$1410万
+$24,432/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1297万
-$24,807/呎
-(24年-06月-06日)</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1416万
-$24,931/呎
-(24年-04月-16日)</t>
+          <t>B | 553呎 (2房)
+$1274万
+$23,042/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1331万
+$26,152/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$895万
+$24,115/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40727,26 +39706,34 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 659呎 (2房)
-$1634万
-$24,795/呎
-(24年-11月-15日)</t>
+          <t>A | 577呎 (2房)
+$1403万
+$24,311/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 523呎 (2房)
-$1464万
-$28,000/呎
-(26年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1409万
-$24,807/呎
-(24年-04月-22日)</t>
+          <t>B | 553呎 (2房)
+$1285万
+$23,242/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1326万
+$26,047/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$893万
+$24,067/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40758,26 +39745,34 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1618万
-$24,671/呎
-(24年-07月-17日)</t>
+          <t>A | 577呎 (2房)
+$1411万
+$24,459/呎
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1292万
-$24,561/呎
-(24年-11月-15日)</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1402万
-$24,684/呎
-(24年-04月-22日)</t>
+          <t>B | 553呎 (2房)
+$1280万
+$23,142/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1321万
+$25,944/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$891万
+$24,019/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40789,26 +39784,34 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1610万
-$24,549/呎
-(24年-05月-10日)</t>
+          <t>A | 577呎 (2房)
+$1389万
+$24,070/呎
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1285万
-$24,439/呎
-(24年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1395万
-$24,561/呎
-(24年-04月-22日)</t>
+          <t>B | 553呎 (2房)
+$1274万
+$23,042/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1315万
+$25,842/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$889万
+$23,971/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40820,26 +39823,34 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1602万
-$24,427/呎
-(24年-05月-13日)</t>
+          <t>A | 577呎 (2房)
+$1382万
+$23,950/呎
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1279万
-$24,317/呎
-(25年-03月-24日)</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1388万
-$24,439/呎
-(24年-04月-22日)</t>
+          <t>B | 553呎 (2房)
+$1274万
+$23,042/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1315万
+$25,842/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$889万
+$23,971/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40851,26 +39862,34 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1587万
-$24,185/呎
+          <t>A | 577呎 (2房)
+$1368万
+$23,713/呎
 (24年-10月-29日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1266万
-$24,076/呎
-(24年-12月-06日)</t>
+          <t>B | 554呎 (2房)
+$1258万
+$22,700/呎
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 568呎 (2房)
-$1374万
-$24,197/呎
-(24年-05月-09日)</t>
+          <t>C | 509呎 (2房)
+$1155万
+$22,700/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$888万
+$23,923/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40882,26 +39901,34 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1579万
-$24,064/呎
-(24年-07月-29日)</t>
+          <t>A | 577呎 (2房)
+$1361万
+$23,595/呎
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1260万
-$23,956/呎
-(24年-11月-22日)</t>
+          <t>B | 553呎 (2房)
+$1252万
+$22,641/呎
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>C | 568呎 (2房)
-$1368万
-$24,076/呎
-(24年-05月-16日)</t>
+          <t>C | 509呎 (2房)
+$1150万
+$22,600/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$886万
+$23,875/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -40913,26 +39940,34 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1571万
-$23,945/呎
-(24年-04月-23日)</t>
+          <t>A | 577呎 (2房)
+$1355万
+$23,477/呎
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1254万
-$23,837/呎
-(24年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1376万
-$24,223/呎
-(24年-04月-22日)</t>
+          <t>B | 554呎 (2房)
+$1295万
+$23,377/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$796万
+$21,445/呎
+(26年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -40944,26 +39979,34 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1563万
-$23,825/呎
-(24年-10月-29日)</t>
+          <t>A | 577呎 (2房)
+$1348万
+$23,361/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1248万
-$23,719/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1354万
-$23,837/呎
-(24年-04月-25日)</t>
+          <t>B | 553呎 (2房)
+$1252万
+$22,641/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1289万
+$25,331/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$882万
+$23,780/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -40975,26 +40018,34 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1555万
-$23,707/呎
-(24年-11月-15日)</t>
+          <t>A | 577呎 (2房)
+$1341万
+$23,244/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
-$1241万
-$23,601/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1347万
-$23,719/呎
-(24年-04月-25日)</t>
+          <t>B | 553呎 (2房)
+$1246万
+$22,541/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1284万
+$25,228/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$880万
+$23,732/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -41006,26 +40057,34 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1547万
-$23,589/呎
-(25年-03月-04日)</t>
+          <t>A | 577呎 (2房)
+$1335万
+$23,129/呎
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 526呎 (2房)
+          <t>B | 554呎 (2房)
 $1235万
-$23,483/呎
-(24年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1355万
-$23,863/呎
-(24年-04月-25日)</t>
+$22,300/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1279万
+$25,128/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$879万
+$23,687/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -41037,26 +40096,34 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1429万
-$21,790/呎
-(25年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>B | 526呎 (2房)
-$1158万
-$22,014/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1250万
-$22,014/呎
-(25年-04月-07日)</t>
+          <t>A | 577呎 (2房)
+$1247万
+$21,606/呎
+(25年-08月-13日)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1332万
+$24,035/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1237万
+$24,307/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$852万
+$22,956/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -41068,26 +40135,34 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1361万
-$20,752/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>B | 526呎 (2房)
-$1103万
-$20,966/呎
-(25年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1191万
-$20,966/呎
+          <t>A | 577呎 (2房)
+$1210万
+$20,976/呎
 (25年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1332万
+$24,035/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1237万
+$24,307/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$852万
+$22,956/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -41099,26 +40174,34 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1335万
-$20,345/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>B | 526呎 (2房)
-$1081万
-$20,555/呎
-(25年-08月-26日)</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1179万
-$20,758/呎
+          <t>A | 577呎 (2房)
+$1198万
+$20,769/呎
 (25年-08月-27日)</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1311万
+$23,668/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1221万
+$23,980/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$842万
+$22,692/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -41130,26 +40213,34 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1331万
-$20,284/呎
-(25年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>B | 526呎 (2房)
-$1078万
-$20,493/呎
-(25年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1176万
-$20,696/呎
-(25年-09月-02日)</t>
+          <t>A | 577呎 (2房)
+$1195万
+$20,706/呎
+(25年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1291万
+$23,309/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1204万
+$23,659/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$832万
+$22,435/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -41161,26 +40252,34 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 656呎 (2房)
-$1327万
-$20,223/呎
-(25年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>B | 526呎 (2房)
-$1075万
-$20,432/呎
-(25年-09月-17日)</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>C | 568呎 (2房)
-$1172万
-$20,634/呎
-(25年-09月-15日)</t>
+          <t>A | 577呎 (2房)
+$1191万
+$20,644/呎
+(25年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1284万
+$23,169/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1199万
+$23,565/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$831万
+$22,390/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -41192,26 +40291,34 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>A | 618呎 (2房)
-$1259万
-$20,371/呎
-(25年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>B | 488呎 (2房)
-$1014万
-$20,787/呎
-(25年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>C | 530呎 (2房)
-$1166万
-$22,000/呎
-(25年-04月-28日)</t>
+          <t>A | 539呎 (2房)
+$1197万
+$22,200/呎
+(25年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>B | 554呎 (2房)
+$1288万
+$23,247/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1195万
+$23,471/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$829万
+$22,345/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -41242,7 +40349,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>5座 销控网格图</t>
+          <t>3B座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -41286,7 +40393,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41296,7 +40403,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41338,12 +40445,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>A | 1994呎 (4+房)
-招标单位
--
-(在售)</t>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 1109呎 (3房)
+$4308万
+$38,846/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
@@ -41357,26 +40464,26 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$3070万
-$33,998/呎
-(24年-04月-19日)</t>
+          <t>A | 659呎 (2房)
+$1799万
+$27,300/呎
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1884万
-$33,400/呎
-(25年-08月-19日)</t>
+          <t>B | 523呎 (2房)
+$1423万
+$27,200/呎
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1978万
-$31,900/呎
-(25年-08月-25日)</t>
+          <t>C | 568呎 (2房)
+$1551万
+$27,300/呎
+(25年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -41388,26 +40495,26 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$3043万
-$33,700/呎
-(25年-11月-17日)</t>
+          <t>A | 659呎 (2房)
+$1766万
+$26,800/呎
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1844万
-$32,700/呎
-(25年-08月-11日)</t>
+          <t>B | 523呎 (2房)
+$1396万
+$26,700/呎
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1941万
-$31,300/呎
-(25年-08月-25日)</t>
+          <t>C | 568呎 (2房)
+$1522万
+$26,800/呎
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -41419,26 +40526,26 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>A | 900呎 (3房)
-$3043万
-$33,812/呎
-(24年-04月-25日)</t>
+          <t>A | 659呎 (2房)
+$1746万
+$26,500/呎
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1827万
-$32,400/呎
-(25年-08月-29日)</t>
+          <t>B | 523呎 (2房)
+$1381万
+$26,400/呎
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1916万
-$30,900/呎
-(25年-08月-14日)</t>
+          <t>C | 568呎 (2房)
+$1505万
+$26,500/呎
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -41450,26 +40557,26 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2935万
-$32,500/呎
-(24年-04月-22日)</t>
+          <t>A | 659呎 (2房)
+$1735万
+$26,323/呎
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1816万
-$32,200/呎
-(25年-08月-21日)</t>
+          <t>B | 523呎 (2房)
+$1371万
+$26,205/呎
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1904万
-$30,712/呎
-(25年-06月-02日)</t>
+          <t>C | 1644呎 (2房)
+$1496万
+$9,099/呎
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -41481,26 +40588,26 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2946万
-$32,623/呎
-(24年-04月-16日)</t>
+          <t>A | 659呎 (2房)
+$1726万
+$26,192/呎
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1805万
-$32,000/呎
-(25年-08月-15日)</t>
+          <t>B | 523呎 (2房)
+$1364万
+$26,075/呎
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1914万
-$30,868/呎
-(24年-11月-04日)</t>
+          <t>C | 568呎 (2房)
+$1488万
+$26,205/呎
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -41512,26 +40619,26 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2899万
-$32,100/呎
-(24年-04月-16日)</t>
+          <t>A | 659呎 (2房)
+$1717万
+$26,062/呎
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1794万
-$31,800/呎
-(25年-08月-15日)</t>
+          <t>B | 523呎 (2房)
+$1357万
+$25,945/呎
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1902万
-$30,684/呎
-(24年-11月-06日)</t>
+          <t>C | 568呎 (2房)
+$1481万
+$26,075/呎
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -41543,26 +40650,26 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2935万
-$32,500/呎
-(25年-08月-15日)</t>
+          <t>A | 659呎 (2房)
+$1709万
+$25,932/呎
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1782万
-$31,600/呎
-(25年-08月-20日)</t>
+          <t>B | 523呎 (2房)
+$1350万
+$25,816/呎
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1870万
-$30,165/呎
-(24年-10月-23日)</t>
+          <t>C | 568呎 (2房)
+$1474万
+$25,945/呎
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -41574,26 +40681,26 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2862万
-$31,700/呎
-(24年-04月-18日)</t>
+          <t>A | 659呎 (2房)
+$1700万
+$25,803/呎
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1771万
-$31,400/呎
-(25年-08月-07日)</t>
+          <t>B | 523呎 (2房)
+$1343万
+$25,688/呎
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1859万
-$29,985/呎
-(24年-09月-17日)</t>
+          <t>C | 568呎 (2房)
+$1466万
+$25,816/呎
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -41605,26 +40712,26 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2872万
-$31,805/呎
-(24年-04月-19日)</t>
+          <t>A | 659呎 (2房)
+$1692万
+$25,675/呎
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1760万
-$31,200/呎
-(25年-08月-14日)</t>
+          <t>B | 523呎 (2房)
+$1337万
+$25,560/呎
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1848万
-$29,807/呎
-(24年-06月-17日)</t>
+          <t>C | 568呎 (2房)
+$1459万
+$25,688/呎
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41636,26 +40743,26 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2946万
-$32,630/呎
-(24年-04月-18日)</t>
+          <t>A | 659呎 (2房)
+$1675万
+$25,421/呎
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1779万
-$31,534/呎
-(24年-05月-14日)</t>
+          <t>B | 523呎 (2房)
+$1324万
+$25,307/呎
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1828万
-$29,482/呎
-(24年-06月-05日)</t>
+          <t>C | 568呎 (2房)
+$1445万
+$25,433/呎
+(24年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -41667,26 +40774,26 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$3180万
-$35,217/呎
-(24年-04月-15日)</t>
+          <t>A | 659呎 (2房)
+$1667万
+$25,294/呎
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1687万
-$29,917/呎
-(24年-04月-25日)</t>
+          <t>B | 523呎 (2房)
+$1317万
+$25,181/呎
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1781万
-$28,732/呎
-(24年-04月-25日)</t>
+          <t>C | 568呎 (2房)
+$1437万
+$25,307/呎
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -41698,26 +40805,26 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2781万
-$30,800/呎
-(24年-04月-18日)</t>
+          <t>A | 659呎 (2房)
+$1659万
+$25,168/呎
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1719万
-$30,482/呎
-(24年-05月-08日)</t>
+          <t>B | 523呎 (2房)
+$1310万
+$25,056/呎
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1790万
-$28,878/呎
-(24年-04月-18日)</t>
+          <t>C | 568呎 (2房)
+$1430万
+$25,181/呎
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -41729,26 +40836,26 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2798万
-$30,982/呎
-(24年-03月-19日)</t>
+          <t>A | 659呎 (2房)
+$1650万
+$25,043/呎
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1709万
-$30,300/呎
-(24年-08月-14日)</t>
+          <t>B | 523呎 (2房)
+$1304万
+$24,931/呎
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1780万
-$28,706/呎
-(24年-04月-24日)</t>
+          <t>C | 568呎 (2房)
+$1423万
+$25,056/呎
+(24年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -41760,26 +40867,26 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2745万
-$30,400/呎
-(24年-04月-10日)</t>
+          <t>A | 659呎 (2房)
+$1642万
+$24,919/呎
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1699万
-$30,119/呎
-(24年-06月-27日)</t>
+          <t>B | 523呎 (2房)
+$1297万
+$24,807/呎
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1769万
-$28,534/呎
-(24年-04月-25日)</t>
+          <t>C | 568呎 (2房)
+$1416万
+$24,931/呎
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -41791,26 +40898,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 903呎 (3房)
-$2764万
-$30,604/呎
-(24年-04月-03日)</t>
+          <t>A | 659呎 (2房)
+$1634万
+$24,795/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 564呎 (2房)
-$1689万
-$29,939/呎
-(24年-05月-14日)</t>
+          <t>B | 523呎 (2房)
+$1464万
+$28,000/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>C | 620呎 (2房)
-$1759万
-$28,364/呎
-(24年-04月-25日)</t>
+          <t>C | 568呎 (2房)
+$1409万
+$24,807/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41822,26 +40929,26 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2867万
-$31,785/呎
-(24年-04月-05日)</t>
+          <t>A | 656呎 (2房)
+$1618万
+$24,671/呎
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1725万
-$30,422/呎
-(24年-05月-16日)</t>
+          <t>B | 526呎 (2房)
+$1292万
+$24,561/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1726万
-$27,885/呎
-(24年-04月-24日)</t>
+          <t>C | 568呎 (2房)
+$1402万
+$24,684/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41853,26 +40960,26 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2697万
-$29,900/呎
-(24年-04月-03日)</t>
+          <t>A | 656呎 (2房)
+$1610万
+$24,549/呎
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1677万
-$29,583/呎
+          <t>B | 526呎 (2房)
+$1285万
+$24,439/呎
 (24年-05月-10日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1716万
-$27,719/呎
-(24年-04月-25日)</t>
+          <t>C | 568呎 (2房)
+$1395万
+$24,561/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41884,26 +40991,26 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2679万
-$29,700/呎
-(24年-04月-16日)</t>
+          <t>A | 656呎 (2房)
+$1602万
+$24,427/呎
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1667万
-$29,407/呎
-(24年-08月-20日)</t>
+          <t>B | 526呎 (2房)
+$1279万
+$24,317/呎
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1725万
-$27,860/呎
-(24年-04月-25日)</t>
+          <t>C | 568呎 (2房)
+$1388万
+$24,439/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -41915,26 +41022,26 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2661万
-$29,500/呎
-(24年-04月-09日)</t>
+          <t>A | 656呎 (2房)
+$1587万
+$24,185/呎
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1627万
-$28,693/呎
-(24年-04月-22日)</t>
+          <t>B | 526呎 (2房)
+$1266万
+$24,076/呎
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1706万
-$27,557/呎
-(24年-04月-22日)</t>
+          <t>C | 568呎 (2房)
+$1374万
+$24,197/呎
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -41946,26 +41053,26 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2634万
-$29,200/呎
-(24年-03月-27日)</t>
+          <t>A | 656呎 (2房)
+$1579万
+$24,064/呎
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1617万
-$28,522/呎
-(24年-04月-24日)</t>
+          <t>B | 526呎 (2房)
+$1260万
+$23,956/呎
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1677万
-$27,091/呎
-(24年-04月-22日)</t>
+          <t>C | 568呎 (2房)
+$1368万
+$24,076/呎
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41977,26 +41084,26 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2713万
-$30,082/呎
-(23年-10月-20日)</t>
+          <t>A | 656呎 (2房)
+$1571万
+$23,945/呎
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1590万
-$28,040/呎
+          <t>B | 526呎 (2房)
+$1254万
+$23,837/呎
+(24年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 568呎 (2房)
+$1376万
+$24,223/呎
 (24年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>C | 619呎 (2房)
-$1700万
-$27,468/呎
-(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -42008,26 +41115,26 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2970万
-$32,924/呎
-(24年-04月-18日)</t>
+          <t>A | 656呎 (2房)
+$1563万
+$23,825/呎
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1598万
-$28,183/呎
-(24年-04月-22日)</t>
+          <t>B | 526呎 (2房)
+$1248万
+$23,719/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1657万
-$26,769/呎
-(24年-04月-23日)</t>
+          <t>C | 568呎 (2房)
+$1354万
+$23,837/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42039,26 +41146,26 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2589万
-$28,700/呎
-(24年-04月-26日)</t>
+          <t>A | 656呎 (2房)
+$1555万
+$23,707/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1588万
-$28,014/呎
-(24年-04月-22日)</t>
+          <t>B | 526呎 (2房)
+$1241万
+$23,601/呎
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1647万
-$26,609/呎
-(24年-04月-26日)</t>
+          <t>C | 568呎 (2房)
+$1347万
+$23,719/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42070,26 +41177,26 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2571万
-$28,500/呎
+          <t>A | 656呎 (2房)
+$1547万
+$23,589/呎
+(25年-03月-04日)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 526呎 (2房)
+$1235万
+$23,483/呎
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>B | 567呎 (2房)
-$1562万
-$27,541/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1637万
-$26,451/呎
-(24年-04月-24日)</t>
+          <t>C | 568呎 (2房)
+$1355万
+$23,863/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42101,26 +41208,26 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2526万
-$28,000/呎
-(24年-05月-14日)</t>
+          <t>A | 656呎 (2房)
+$1429万
+$21,790/呎
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1442万
-$25,438/呎
-(25年-03月-26日)</t>
+          <t>B | 526呎 (2房)
+$1158万
+$22,014/呎
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1530万
-$24,714/呎
-(25年-03月-12日)</t>
+          <t>C | 568呎 (2房)
+$1250万
+$22,014/呎
+(25年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -42132,26 +41239,26 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$2089万
-$23,156/呎
-(25年-04月-15日)</t>
+          <t>A | 656呎 (2房)
+$1361万
+$20,752/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1299万
-$22,917/呎
-(25年-04月-15日)</t>
+          <t>B | 526呎 (2房)
+$1103万
+$20,966/呎
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1391万
-$22,468/呎
-(25年-04月-15日)</t>
+          <t>C | 568呎 (2房)
+$1191万
+$20,966/呎
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -42163,26 +41270,26 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$1989万
-$22,053/呎
-(25年-04月-15日)</t>
+          <t>A | 656呎 (2房)
+$1335万
+$20,345/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1238万
-$21,826/呎
-(25年-03月-12日)</t>
+          <t>B | 526呎 (2房)
+$1081万
+$20,555/呎
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1337万
-$21,604/呎
-(25年-08月-14日)</t>
+          <t>C | 568呎 (2房)
+$1179万
+$20,758/呎
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -42194,26 +41301,26 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$1983万
-$21,987/呎
-(25年-08月-29日)</t>
+          <t>A | 656呎 (2房)
+$1331万
+$20,284/呎
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1234万
-$21,760/呎
-(25年-08月-13日)</t>
+          <t>B | 526呎 (2房)
+$1078万
+$20,493/呎
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1333万
-$21,539/呎
-(25年-08月-11日)</t>
+          <t>C | 568呎 (2房)
+$1176万
+$20,696/呎
+(25年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -42225,26 +41332,26 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 902呎 (3房)
-$1977万
-$21,921/呎
-(25年-09月-04日)</t>
+          <t>A | 656呎 (2房)
+$1327万
+$20,223/呎
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>B | 567呎 (2房)
-$1230万
-$21,695/呎
-(25年-08月-29日)</t>
+          <t>B | 526呎 (2房)
+$1075万
+$20,432/呎
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>C | 619呎 (2房)
-$1329万
-$21,474/呎
-(25年-08月-22日)</t>
+          <t>C | 568呎 (2房)
+$1172万
+$20,634/呎
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -42256,26 +41363,26 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>A | 869呎 (3房)
-$1921万
-$22,106/呎
-(25年-12月-04日)</t>
+          <t>A | 618呎 (2房)
+$1259万
+$20,371/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>B | 529呎 (2房)
-$1165万
-$22,027/呎
-(25年-03月-26日)</t>
+          <t>B | 488呎 (2房)
+$1014万
+$20,787/呎
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>C | 597呎 (2房)
-$1292万
-$21,644/呎
-(25年-08月-22日)</t>
+          <t>C | 530呎 (2房)
+$1166万
+$22,000/呎
+(25年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -42306,7 +41413,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>6座 销控网格图</t>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -42404,7 +41511,7 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 2103呎 (4+房)
+          <t>A | 1994呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -42421,26 +41528,26 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3515万
-$37,000/呎
-(24年-04月-18日)</t>
+          <t>A | 903呎 (3房)
+$3070万
+$33,998/呎
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2761万
-$35,350/呎
-(24年-04月-26日)</t>
+          <t>B | 564呎 (2房)
+$1884万
+$33,400/呎
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3133万
-$34,700/呎
-(24年-04月-23日)</t>
+          <t>C | 620呎 (2房)
+$1978万
+$31,900/呎
+(25年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -42452,26 +41559,26 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3397万
-$35,754/呎
-(24年-04月-24日)</t>
+          <t>A | 903呎 (3房)
+$3043万
+$33,700/呎
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2706万
-$34,643/呎
-(24年-04月-24日)</t>
+          <t>B | 564呎 (2房)
+$1844万
+$32,700/呎
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3101万
-$34,340/呎
-(24年-04月-24日)</t>
+          <t>C | 620呎 (2房)
+$1941万
+$31,300/呎
+(25年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -42483,26 +41590,26 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3473万
-$36,554/呎
-(24年-04月-11日)</t>
+          <t>A | 900呎 (3房)
+$3043万
+$33,812/呎
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2773万
-$35,510/呎
-(24年-04月-11日)</t>
+          <t>B | 564呎 (2房)
+$1827万
+$32,400/呎
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3043万
-$33,700/呎
-(24年-04月-18日)</t>
+          <t>C | 620呎 (2房)
+$1916万
+$30,900/呎
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -42514,26 +41621,26 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3914万
-$41,198/呎
-(23年-03月-10日)</t>
+          <t>A | 903呎 (3房)
+$2935万
+$32,500/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2666万
-$34,138/呎
-(24年-04月-10日)</t>
+          <t>B | 564呎 (2房)
+$1816万
+$32,200/呎
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3025万
-$33,500/呎
-(24年-04月-12日)</t>
+          <t>C | 620呎 (2房)
+$1904万
+$30,712/呎
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -42545,26 +41652,26 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3539万
-$37,254/呎
-(23年-03月-06日)</t>
+          <t>A | 903呎 (3房)
+$2946万
+$32,623/呎
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2646万
-$33,880/呎
-(24年-04月-05日)</t>
+          <t>B | 564呎 (2房)
+$1805万
+$32,000/呎
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3010万
-$33,330/呎
-(24年-04月-05日)</t>
+          <t>C | 620呎 (2房)
+$1914万
+$30,868/呎
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -42576,26 +41683,26 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3711万
-$39,061/呎
-(23年-03月-06日)</t>
+          <t>A | 903呎 (3房)
+$2899万
+$32,100/呎
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2609万
-$33,400/呎
-(24年-04月-08日)</t>
+          <t>B | 564呎 (2房)
+$1794万
+$31,800/呎
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2989万
-$33,100/呎
-(24年-04月-05日)</t>
+          <t>C | 620呎 (2房)
+$1902万
+$30,684/呎
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -42607,26 +41714,26 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3671万
-$38,638/呎
-(23年-03月-21日)</t>
+          <t>A | 903呎 (3房)
+$2935万
+$32,500/呎
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2708万
-$34,674/呎
-(24年-04月-11日)</t>
+          <t>B | 564呎 (2房)
+$1782万
+$31,600/呎
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3340万
-$36,992/呎
-(24年-04月-12日)</t>
+          <t>C | 620呎 (2房)
+$1870万
+$30,165/呎
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -42638,26 +41745,26 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3223万
-$33,928/呎
-(25年-09月-18日)</t>
+          <t>A | 903呎 (3房)
+$2862万
+$31,700/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2708万
-$34,677/呎
-(24年-04月-12日)</t>
+          <t>B | 564呎 (2房)
+$1771万
+$31,400/呎
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2953万
-$32,700/呎
-(24年-04月-18日)</t>
+          <t>C | 620呎 (2房)
+$1859万
+$29,985/呎
+(24年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -42669,26 +41776,26 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3211万
-$33,800/呎
-(25年-11月-20日)</t>
+          <t>A | 903呎 (3房)
+$2872万
+$31,805/呎
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2562万
-$32,800/呎
-(25年-12月-30日)</t>
+          <t>B | 564呎 (2房)
+$1760万
+$31,200/呎
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3046万
-$33,734/呎
-(24年-04月-05日)</t>
+          <t>C | 620呎 (2房)
+$1848万
+$29,807/呎
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -42700,26 +41807,26 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3618万
-$38,084/呎
-(23年-02月-02日)</t>
+          <t>A | 903呎 (3房)
+$2946万
+$32,630/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2530万
-$32,399/呎
-(23年-05月-25日)</t>
+          <t>B | 564呎 (2房)
+$1779万
+$31,534/呎
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2888万
-$31,977/呎
-(24年-04月-02日)</t>
+          <t>C | 620呎 (2房)
+$1828万
+$29,482/呎
+(24年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -42731,26 +41838,26 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3154万
-$33,200/呎
-(25年-08月-25日)</t>
+          <t>A | 903呎 (3房)
+$3180万
+$35,217/呎
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2550万
-$32,650/呎
-(23年-03月-14日)</t>
+          <t>B | 564呎 (2房)
+$1687万
+$29,917/呎
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2938万
-$32,538/呎
-(23年-05月-19日)</t>
+          <t>C | 620呎 (2房)
+$1781万
+$28,732/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42762,26 +41869,26 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3480万
-$36,628/呎
-(22年-12月-13日)</t>
+          <t>A | 903呎 (3房)
+$2781万
+$30,800/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2534万
-$32,445/呎
-(23年-03月-07日)</t>
+          <t>B | 564呎 (2房)
+$1719万
+$30,482/呎
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$3217万
-$35,626/呎
-(23年-06月-15日)</t>
+          <t>C | 620呎 (2房)
+$1790万
+$28,878/呎
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -42793,26 +41900,26 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3221万
-$33,902/呎
-(23年-02月-02日)</t>
+          <t>A | 903呎 (3房)
+$2798万
+$30,982/呎
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2491万
-$31,900/呎
-(25年-11月-24日)</t>
+          <t>B | 564呎 (2房)
+$1709万
+$30,300/呎
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2936万
-$32,514/呎
-(23年-04月-13日)</t>
+          <t>C | 620呎 (2房)
+$1780万
+$28,706/呎
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42824,26 +41931,26 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3200万
-$33,687/呎
-(23年-02月-02日)</t>
+          <t>A | 903呎 (3房)
+$2745万
+$30,400/呎
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2476万
-$31,700/呎
-(25年-11月-12日)</t>
+          <t>B | 564呎 (2房)
+$1699万
+$30,119/呎
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2835万
-$31,400/呎
-(25年-08月-27日)</t>
+          <t>C | 620呎 (2房)
+$1769万
+$28,534/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42855,26 +41962,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 950呎 (3房)
-$3564万
-$37,513/呎
-(23年-01月-13日)</t>
+          <t>A | 903呎 (3房)
+$2764万
+$30,604/呎
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 781呎 (3房)
-$2460万
-$31,500/呎
-(25年-12月-15日)</t>
+          <t>B | 564呎 (2房)
+$1689万
+$29,939/呎
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>C | 903呎 (3房)
-$2817万
-$31,200/呎
-(25年-08月-29日)</t>
+          <t>C | 620呎 (2房)
+$1759万
+$28,364/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42886,26 +41993,26 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$3334万
-$35,165/呎
-(22年-12月-08日)</t>
+          <t>A | 902呎 (3房)
+$2867万
+$31,785/呎
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2980万
-$38,010/呎
-(22年-12月-28日)</t>
+          <t>B | 567呎 (2房)
+$1725万
+$30,422/呎
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2742万
-$30,399/呎
-(25年-03月-24日)</t>
+          <t>C | 619呎 (2房)
+$1726万
+$27,885/呎
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -42917,26 +42024,26 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$3268万
-$34,473/呎
-(22年-12月-13日)</t>
+          <t>A | 902呎 (3房)
+$2697万
+$29,900/呎
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2465万
-$31,444/呎
-(23年-02月-09日)</t>
+          <t>B | 567呎 (2房)
+$1677万
+$29,583/呎
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$3120万
-$34,591/呎
-(23年-02月-09日)</t>
+          <t>C | 619呎 (2房)
+$1716万
+$27,719/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42948,26 +42055,26 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$3181万
-$33,555/呎
-(23年-02月-10日)</t>
+          <t>A | 902呎 (3房)
+$2679万
+$29,700/呎
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2446万
-$31,200/呎
-(22年-12月-08日)</t>
+          <t>B | 567呎 (2房)
+$1667万
+$29,407/呎
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$3028万
-$33,568/呎
-(23年-02月-28日)</t>
+          <t>C | 619呎 (2房)
+$1725万
+$27,860/呎
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -42979,26 +42086,26 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$3002万
-$31,667/呎
-(23年-02月-07日)</t>
+          <t>A | 902呎 (3房)
+$2661万
+$29,500/呎
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2447万
-$31,211/呎
-(23年-04月-17日)</t>
+          <t>B | 567呎 (2房)
+$1627万
+$28,693/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2760万
-$30,599/呎
-(22年-12月-22日)</t>
+          <t>C | 619呎 (2房)
+$1706万
+$27,557/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -43010,26 +42117,26 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2967万
-$31,300/呎
-(25年-10月-30日)</t>
+          <t>A | 902呎 (3房)
+$2634万
+$29,200/呎
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2564万
-$32,702/呎
-(23年-04月-03日)</t>
+          <t>B | 567呎 (2房)
+$1617万
+$28,522/呎
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2756万
-$30,550/呎
-(22年-12月-08日)</t>
+          <t>C | 619呎 (2房)
+$1677万
+$27,091/呎
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -43041,26 +42148,26 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2948万
-$31,100/呎
-(25年-08月-29日)</t>
+          <t>A | 902呎 (3房)
+$2713万
+$30,082/呎
+(23年-10月-20日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2376万
-$30,300/呎
-(22年-12月-08日)</t>
+          <t>B | 567呎 (2房)
+$1590万
+$28,040/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$3070万
-$34,034/呎
-(22年-12月-08日)</t>
+          <t>C | 619呎 (2房)
+$1700万
+$27,468/呎
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -43072,26 +42179,26 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2959万
-$31,209/呎
-(23年-02月-06日)</t>
+          <t>A | 902呎 (3房)
+$2970万
+$32,924/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2670万
-$34,051/呎
-(22年-12月-08日)</t>
+          <t>B | 567呎 (2房)
+$1598万
+$28,183/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2733万
-$30,300/呎
-(23年-06月-01日)</t>
+          <t>C | 619呎 (2房)
+$1657万
+$26,769/呎
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -43103,26 +42210,26 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2920万
-$30,800/呎
-(25年-10月-08日)</t>
+          <t>A | 902呎 (3房)
+$2589万
+$28,700/呎
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2344万
-$29,900/呎
-(25年-10月-30日)</t>
+          <t>B | 567呎 (2房)
+$1588万
+$28,014/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2670万
-$29,600/呎
-(25年-10月-09日)</t>
+          <t>C | 619呎 (2房)
+$1647万
+$26,609/呎
+(24年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -43134,26 +42241,26 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$3151万
-$33,235/呎
-(24年-03月-13日)</t>
+          <t>A | 902呎 (3房)
+$2571万
+$28,500/呎
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2398万
-$30,590/呎
-(24年-01月-17日)</t>
+          <t>B | 567呎 (2房)
+$1562万
+$27,541/呎
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2670万
-$29,596/呎
-(24年-04月-18日)</t>
+          <t>C | 619呎 (2房)
+$1637万
+$26,451/呎
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -43165,26 +42272,26 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2702万
-$28,500/呎
-(24年-04月-25日)</t>
+          <t>A | 902呎 (3房)
+$2526万
+$28,000/呎
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$2242万
-$28,600/呎
-(24年-04月-18日)</t>
+          <t>B | 567呎 (2房)
+$1442万
+$25,438/呎
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2598万
-$28,800/呎
-(24年-04月-23日)</t>
+          <t>C | 619呎 (2房)
+$1530万
+$24,714/呎
+(25年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -43196,26 +42303,26 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2291万
-$24,163/呎
-(25年-03月-11日)</t>
+          <t>A | 902呎 (3房)
+$2089万
+$23,156/呎
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$1850万
-$23,596/呎
-(25年-03月-24日)</t>
+          <t>B | 567呎 (2房)
+$1299万
+$22,917/呎
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2152万
-$23,856/呎
-(25年-03月-11日)</t>
+          <t>C | 619呎 (2房)
+$1391万
+$22,468/呎
+(25年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -43227,26 +42334,26 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2141万
-$22,582/呎
-(25年-04月-16日)</t>
+          <t>A | 902呎 (3房)
+$1989万
+$22,053/呎
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$1745万
-$22,260/呎
-(25年-04月-16日)</t>
+          <t>B | 567呎 (2房)
+$1238万
+$21,826/呎
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2030万
-$22,506/呎
-(25年-08月-15日)</t>
+          <t>C | 619呎 (2房)
+$1337万
+$21,604/呎
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -43258,26 +42365,26 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2130万
-$22,469/呎
-(25年-08月-14日)</t>
+          <t>A | 902呎 (3房)
+$1983万
+$21,987/呎
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$1740万
-$22,194/呎
-(25年-06月-17日)</t>
+          <t>B | 567呎 (2房)
+$1234万
+$21,760/呎
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2024万
-$22,438/呎
-(25年-08月-15日)</t>
+          <t>C | 619呎 (2房)
+$1333万
+$21,539/呎
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -43289,26 +42396,26 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 948呎 (3房)
-$2119万
-$22,357/呎
-(25年-08月-14日)</t>
+          <t>A | 902呎 (3房)
+$1977万
+$21,921/呎
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>B | 784呎 (3房)
-$1735万
-$22,127/呎
-(25年-06月-17日)</t>
+          <t>B | 567呎 (2房)
+$1230万
+$21,695/呎
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>C | 902呎 (3房)
-$2018万
-$22,371/呎
-(25年-09月-18日)</t>
+          <t>C | 619呎 (2房)
+$1329万
+$21,474/呎
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -43320,26 +42427,26 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>A | 915呎 (3房)
-$2060万
-$22,518/呎
-(25年-09月-22日)</t>
+          <t>A | 869呎 (3房)
+$1921万
+$22,106/呎
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>B | 738呎 (3房)
-$1680万
-$22,764/呎
-(25年-04月-15日)</t>
+          <t>B | 529呎 (2房)
+$1165万
+$22,027/呎
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>C | 869呎 (3房)
-$1960万
-$22,560/呎
-(25年-10月-09日)</t>
+          <t>C | 597呎 (2房)
+$1292万
+$21,644/呎
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -43364,12 +42471,13 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>8座 销控网格图</t>
+          <t>6座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -43408,22 +42516,22 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43453,6 +42561,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -43460,15 +42573,16 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>A | 2639呎 (4+房)
-$16224万
-$61,476/呎
-(23年-09月-28日)</t>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 2103呎 (4+房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -43478,18 +42592,26 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$6543万
-$42,959/呎
-(24年-12月-30日)</t>
+          <t>A | 950呎 (3房)
+$3515万
+$37,000/呎
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4953万
-$41,725/呎
-(24年-04月-24日)</t>
+          <t>B | 781呎 (3房)
+$2761万
+$35,350/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3133万
+$34,700/呎
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -43501,18 +42623,26 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5742万
-$37,700/呎
-(25年-09月-23日)</t>
+          <t>A | 950呎 (3房)
+$3397万
+$35,754/呎
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4522万
-$38,100/呎
-(24年-04月-16日)</t>
+          <t>B | 781呎 (3房)
+$2706万
+$34,643/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3101万
+$34,340/呎
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -43524,18 +42654,26 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5966万
-$39,174/呎
-(25年-10月-15日)</t>
+          <t>A | 950呎 (3房)
+$3473万
+$36,554/呎
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$5074万
-$42,743/呎
-(24年-04月-03日)</t>
+          <t>B | 781呎 (3房)
+$2773万
+$35,510/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3043万
+$33,700/呎
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -43547,18 +42685,26 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5528万
-$36,300/呎
-(25年-01月-28日)</t>
+          <t>A | 950呎 (3房)
+$3914万
+$41,198/呎
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4439万
-$37,400/呎
-(25年-12月-15日)</t>
+          <t>B | 781呎 (3房)
+$2666万
+$34,138/呎
+(24年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3025万
+$33,500/呎
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -43570,18 +42716,26 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5498万
-$36,100/呎
-(24年-12月-18日)</t>
+          <t>A | 950呎 (3房)
+$3539万
+$37,254/呎
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4439万
-$37,400/呎
-(24年-04月-17日)</t>
+          <t>B | 781呎 (3房)
+$2646万
+$33,880/呎
+(24年-04月-05日)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3010万
+$33,330/呎
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43593,18 +42747,26 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5969万
-$39,190/呎
-(24年-10月-04日)</t>
+          <t>A | 950呎 (3房)
+$3711万
+$39,061/呎
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4380万
-$36,900/呎
-(25年-09月-29日)</t>
+          <t>B | 781呎 (3房)
+$2609万
+$33,400/呎
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2989万
+$33,100/呎
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43616,18 +42778,26 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5986万
-$39,307/呎
-(24年-04月-15日)</t>
+          <t>A | 950呎 (3房)
+$3671万
+$38,638/呎
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4356万
-$36,700/呎
-(25年-11月-25日)</t>
+          <t>B | 781呎 (3房)
+$2708万
+$34,674/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3340万
+$36,992/呎
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -43639,18 +42809,26 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5840万
-$38,346/呎
-(24年-11月-20日)</t>
+          <t>A | 950呎 (3房)
+$3223万
+$33,928/呎
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4321万
-$36,400/呎
-(25年-12月-09日)</t>
+          <t>B | 781呎 (3房)
+$2708万
+$34,677/呎
+(24年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2953万
+$32,700/呎
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -43662,18 +42840,26 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5457万
-$35,830/呎
-(24年-11月-20日)</t>
+          <t>A | 950呎 (3房)
+$3211万
+$33,800/呎
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4285万
-$36,100/呎
-(23年-03月-23日)</t>
+          <t>B | 781呎 (3房)
+$2562万
+$32,800/呎
+(25年-12月-30日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3046万
+$33,734/呎
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -43685,18 +42871,26 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5393万
-$35,410/呎
-(24年-11月-20日)</t>
+          <t>A | 950呎 (3房)
+$3618万
+$38,084/呎
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4500万
-$37,911/呎
-(22年-12月-08日)</t>
+          <t>B | 781呎 (3房)
+$2530万
+$32,399/呎
+(23年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2888万
+$31,977/呎
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -43708,18 +42902,26 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5313万
-$34,882/呎
-(23年-03月-03日)</t>
+          <t>A | 950呎 (3房)
+$3154万
+$33,200/呎
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 1135呎 (3房)
-$4214万
-$37,126/呎
-(26年-05月-20日)</t>
+          <t>B | 781呎 (3房)
+$2550万
+$32,650/呎
+(23年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2938万
+$32,538/呎
+(23年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -43731,18 +42933,26 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5474万
-$35,942/呎
-(24年-11月-12日)</t>
+          <t>A | 950呎 (3房)
+$3480万
+$36,628/呎
+(22年-12月-13日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4851万
-$40,867/呎
-(23年-03月-20日)</t>
+          <t>B | 781呎 (3房)
+$2534万
+$32,445/呎
+(23年-03月-07日)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$3217万
+$35,626/呎
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -43754,18 +42964,26 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5387万
-$35,369/呎
-(24年-10月-10日)</t>
+          <t>A | 950呎 (3房)
+$3221万
+$33,902/呎
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4330万
-$36,477/呎
-(23年-02月-22日)</t>
+          <t>B | 781呎 (3房)
+$2491万
+$31,900/呎
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2936万
+$32,514/呎
+(23年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -43777,18 +42995,26 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$4980万
-$32,700/呎
-(24年-04月-18日)</t>
+          <t>A | 950呎 (3房)
+$3200万
+$33,687/呎
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$3960万
-$33,361/呎
-(23年-02月-22日)</t>
+          <t>B | 781呎 (3房)
+$2476万
+$31,700/呎
+(25年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2835万
+$31,400/呎
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -43800,18 +43026,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
-$5364万
-$35,217/呎
-(24年-03月-13日)</t>
+          <t>A | 950呎 (3房)
+$3564万
+$37,513/呎
+(23年-01月-13日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 1187呎 (3房)
-$4095万
-$34,500/呎
-(25年-12月-03日)</t>
+          <t>B | 781呎 (3房)
+$2460万
+$31,500/呎
+(25年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 903呎 (3房)
+$2817万
+$31,200/呎
+(25年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -43823,18 +43057,26 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4926万
-$32,300/呎
-(24年-04月-10日)</t>
+          <t>A | 948呎 (3房)
+$3334万
+$35,165/呎
+(22年-12月-08日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4206万
-$35,494/呎
-(23年-05月-17日)</t>
+          <t>B | 784呎 (3房)
+$2980万
+$38,010/呎
+(22年-12月-28日)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2742万
+$30,399/呎
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -43846,18 +43088,26 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4956万
-$32,498/呎
-(23年-07月-11日)</t>
+          <t>A | 948呎 (3房)
+$3268万
+$34,473/呎
+(22年-12月-13日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4468万
-$37,705/呎
-(22年-12月-08日)</t>
+          <t>B | 784呎 (3房)
+$2465万
+$31,444/呎
+(23年-02月-09日)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3120万
+$34,591/呎
+(23年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -43869,18 +43119,26 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$5002万
-$32,800/呎
-(25年-09月-09日)</t>
+          <t>A | 948呎 (3房)
+$3181万
+$33,555/呎
+(23年-02月-10日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4005万
-$33,800/呎
-(26年-02月-13日)</t>
+          <t>B | 784呎 (3房)
+$2446万
+$31,200/呎
+(22年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3028万
+$33,568/呎
+(23年-02月-28日)</t>
         </is>
       </c>
     </row>
@@ -43892,18 +43150,26 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$5265万
-$34,525/呎
-(23年-02月-15日)</t>
+          <t>A | 948呎 (3房)
+$3002万
+$31,667/呎
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4092万
-$34,531/呎
-(23年-02月-15日)</t>
+          <t>B | 784呎 (3房)
+$2447万
+$31,211/呎
+(23年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2760万
+$30,599/呎
+(22年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -43915,18 +43181,26 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4773万
+          <t>A | 948呎 (3房)
+$2967万
 $31,300/呎
-(24年-05月-23日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$3922万
-$33,100/呎
-(25年-10月-03日)</t>
+          <t>B | 784呎 (3房)
+$2564万
+$32,702/呎
+(23年-04月-03日)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2756万
+$30,550/呎
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -43938,18 +43212,26 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$5261万
-$34,497/呎
-(25年-11月-11日)</t>
+          <t>A | 948呎 (3房)
+$2948万
+$31,100/呎
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4100万
-$34,599/呎
-(23年-02月-23日)</t>
+          <t>B | 784呎 (3房)
+$2376万
+$30,300/呎
+(22年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$3070万
+$34,034/呎
+(22年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -43961,18 +43243,26 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$5101万
-$33,450/呎
-(22年-12月-12日)</t>
+          <t>A | 948呎 (3房)
+$2959万
+$31,209/呎
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4337万
-$36,596/呎
-(23年-03月-03日)</t>
+          <t>B | 784呎 (3房)
+$2670万
+$34,051/呎
+(22年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2733万
+$30,300/呎
+(23年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -43984,18 +43274,26 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4712万
-$30,900/呎
-(24年-04月-25日)</t>
+          <t>A | 948呎 (3房)
+$2920万
+$30,800/呎
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4039万
-$34,084/呎
-(23年-03月-03日)</t>
+          <t>B | 784呎 (3房)
+$2344万
+$29,900/呎
+(25年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2670万
+$29,600/呎
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -44007,18 +43305,26 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$5119万
-$33,566/呎
-(25年-09月-29日)</t>
+          <t>A | 948呎 (3房)
+$3151万
+$33,235/呎
+(24年-03月-13日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$4317万
-$36,433/呎
-(23年-03月-03日)</t>
+          <t>B | 784呎 (3房)
+$2398万
+$30,590/呎
+(24年-01月-17日)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2670万
+$29,596/呎
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -44030,18 +43336,26 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4888万
-$32,050/呎
-(24年-11月-26日)</t>
+          <t>A | 948呎 (3房)
+$2702万
+$28,500/呎
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$3389万
+          <t>B | 784呎 (3房)
+$2242万
 $28,600/呎
-(24年-04月-02日)</t>
+(24年-04月-18日)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2598万
+$28,800/呎
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -44053,18 +43367,26 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4333万
-$28,410/呎
-(25年-04月-16日)</t>
+          <t>A | 948呎 (3房)
+$2291万
+$24,163/呎
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$3300万
-$27,848/呎
-(24年-04月-18日)</t>
+          <t>B | 784呎 (3房)
+$1850万
+$23,596/呎
+(25年-03月-24日)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2152万
+$23,856/呎
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -44076,18 +43398,26 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4049万
-$26,552/呎
-(25年-11月-11日)</t>
+          <t>A | 948呎 (3房)
+$2141万
+$22,582/呎
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$3261万
-$27,522/呎
-(24年-05月-30日)</t>
+          <t>B | 784呎 (3房)
+$1745万
+$22,260/呎
+(25年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2030万
+$22,506/呎
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -44099,18 +43429,26 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4380万
-$28,720/呎
-(25年-12月-23日)</t>
+          <t>A | 948呎 (3房)
+$2130万
+$22,469/呎
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$3072万
-$25,920/呎
-(25年-03月-21日)</t>
+          <t>B | 784呎 (3房)
+$1740万
+$22,194/呎
+(25年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2024万
+$22,438/呎
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -44122,18 +43460,26 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>A | 1525呎 (3房)
-$4376万
-$28,692/呎
-(26年-01月-22日)</t>
+          <t>A | 948呎 (3房)
+$2119万
+$22,357/呎
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
-$2978万
-$25,131/呎
-(24年-05月-10日)</t>
+          <t>B | 784呎 (3房)
+$1735万
+$22,127/呎
+(25年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 902呎 (3房)
+$2018万
+$22,371/呎
+(25年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -44145,18 +43491,26 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>A | 1466呎 (3房)
-$4217万
-$28,768/呎
-(26年-03月-23日)</t>
+          <t>A | 915呎 (3房)
+$2060万
+$22,518/呎
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>B | 1146呎 (3房)
-$2904万
-$25,336/呎
-(25年-10月-17日)</t>
+          <t>B | 738呎 (3房)
+$1680万
+$22,764/呎
+(25年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>C | 869呎 (3房)
+$1960万
+$22,560/呎
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -44175,24 +43529,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>沄璟 - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -44223,117 +43576,764 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="30" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="26" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/屋号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Harbour Breeze</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Harbour Light</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Harbour Wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Mansion A</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 2639呎 (4+房)
+$16224万
+$61,476/呎
+(23年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$6543万
+$42,959/呎
+(24年-12月-30日)</t>
+        </is>
+      </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Mansion A (Harbour Light)
-4636呎 (4+房)
-(24年-06月-28日)
-$3.40亿
-$73,339/呎</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr"/>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Mansion B</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Mansion B (Harbour Breeze)
-4294呎 (4+房)
-(暂停销售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr"/>
-      <c r="D7" s="31" t="inlineStr"/>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Mansion C</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr"/>
-      <c r="C8" s="31" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Mansion C (Harbour Wave)
-4850呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+          <t>B | 1187呎 (3房)
+$4953万
+$41,725/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5742万
+$37,700/呎
+(25年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4522万
+$38,100/呎
+(24年-04月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5966万
+$39,174/呎
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$5074万
+$42,743/呎
+(24年-04月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5528万
+$36,300/呎
+(25年-01月-28日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4439万
+$37,400/呎
+(25年-12月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5498万
+$36,100/呎
+(24年-12月-18日)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4439万
+$37,400/呎
+(24年-04月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5969万
+$39,190/呎
+(24年-10月-04日)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4380万
+$36,900/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5986万
+$39,307/呎
+(24年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4356万
+$36,700/呎
+(25年-11月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5840万
+$38,346/呎
+(24年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4321万
+$36,400/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5457万
+$35,830/呎
+(24年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4285万
+$36,100/呎
+(23年-03月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5393万
+$35,410/呎
+(24年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4500万
+$37,911/呎
+(22年-12月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5313万
+$34,882/呎
+(23年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1135呎 (3房)
+$4214万
+$37,126/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5474万
+$35,942/呎
+(24年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4851万
+$40,867/呎
+(23年-03月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5387万
+$35,369/呎
+(24年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4330万
+$36,477/呎
+(23年-02月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$4980万
+$32,700/呎
+(24年-04月-18日)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$3960万
+$33,361/呎
+(23年-02月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1523呎 (3房)
+$5364万
+$35,217/呎
+(24年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1187呎 (3房)
+$4095万
+$34,500/呎
+(25年-12月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4926万
+$32,300/呎
+(24年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4206万
+$35,494/呎
+(23年-05月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4956万
+$32,498/呎
+(23年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4468万
+$37,705/呎
+(22年-12月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5002万
+$32,800/呎
+(25年-09月-09日)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4005万
+$33,800/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5265万
+$34,525/呎
+(23年-02月-15日)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4092万
+$34,531/呎
+(23年-02月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4773万
+$31,300/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3922万
+$33,100/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5261万
+$34,497/呎
+(25年-11月-11日)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4100万
+$34,599/呎
+(23年-02月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5101万
+$33,450/呎
+(22年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4337万
+$36,596/呎
+(23年-03月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4712万
+$30,900/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4039万
+$34,084/呎
+(23年-03月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$5119万
+$33,566/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$4317万
+$36,433/呎
+(23年-03月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4888万
+$32,050/呎
+(24年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3389万
+$28,600/呎
+(24年-04月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4333万
+$28,410/呎
+(25年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3300万
+$27,848/呎
+(24年-04月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4049万
+$26,552/呎
+(25年-11月-11日)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3261万
+$27,522/呎
+(24年-05月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4380万
+$28,720/呎
+(25年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$3072万
+$25,920/呎
+(25年-03月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 1525呎 (3房)
+$4376万
+$28,692/呎
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 1185呎 (3房)
+$2978万
+$25,131/呎
+(24年-05月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>A | 1466呎 (3房)
+$4217万
+$28,768/呎
+(26年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>B | 1146呎 (3房)
+$2904万
+$25,336/呎
+(25年-10月-17日)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1855</v>
+        <v>1909</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>92948700</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>50107</v>
+        <v>48690</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>92948700</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>50107</v>
+        <v>48690</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>43080000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>38846</v>
+        <v>38671</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>43080000</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>38846</v>
+        <v>38671</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -38427,9 +38427,9 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 1855呎 (4+房)
+          <t>A | 1909呎 (4+房)
 $9295万
-$50,107/呎
+$48,690/呎
 (25年-07月-09日)</t>
         </is>
       </c>
@@ -40276,9 +40276,9 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>A | 1109呎 (3房)
+          <t>A | 1114呎 (3房)
 $4308万
-$38,846/呎
+$38,671/呎
 (26年-08月-03日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>14514800</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>26200</v>
+        <v>26247</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>14514800</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>26200</v>
+        <v>26247</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -38905,12 +38905,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39075,9 +39075,9 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1451万
-$26,200/呎
+$26,247/呎
 (26年-08月-09日)</t>
         </is>
       </c>
@@ -40009,12 +40009,12 @@
 (25年-08月-27日)</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1311万
 $23,668/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
@@ -40126,12 +40126,12 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
 $1288万
 $23,247/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1870</v>
+        <v>1816</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1806,14 +1806,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
         <v>92299060</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>49358</v>
+        <v>50825</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>92299060</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>49358</v>
+        <v>50825</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>13240600</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>23900</v>
+        <v>23943</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>13240600</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>23900</v>
+        <v>23943</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>12852800</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>23200</v>
+        <v>23242</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>12852800</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>23200</v>
+        <v>23242</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>12742000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>23000</v>
+        <v>23042</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>12742000</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>23000</v>
+        <v>23042</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>11984000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>21632</v>
+        <v>21671</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>11984000</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>21632</v>
+        <v>21671</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
@@ -16005,34 +16005,34 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>12878900</v>
+        <v>11591000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>23247</v>
+        <v>20922</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>11591010</v>
+        <v>11591000</v>
       </c>
       <c r="L243" s="5" t="n">
         <v>20922</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
@@ -37519,10 +37519,10 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 1870呎 (4+房)
+          <t>B | 1816呎 (4+房)
 $9230万
-$49,358/呎
-(26年-07月-27日)</t>
+$50,825/呎
+(26年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -38905,7 +38905,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38915,7 +38915,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39114,9 +39114,9 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1324万
-$23,900/呎
+$23,943/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -39309,9 +39309,9 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1285万
-$23,200/呎
+$23,242/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -39348,9 +39348,9 @@
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1274万
-$23,000/呎
+$23,042/呎
 (26年-05月-29日)</t>
         </is>
       </c>
@@ -39933,9 +39933,9 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1198万
-$21,632/呎
+$21,671/呎
 (26年-08月-10日)</t>
         </is>
       </c>
@@ -40126,12 +40126,12 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
-$1288万
-$23,247/呎
-(在售)</t>
+$1159万
+$20,922/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2088</v>
+        <v>2034</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1868,14 +1868,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
         <v>113302860</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>54264</v>
+        <v>55704</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>113302860</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>54264</v>
+        <v>55704</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -15018,14 +15018,14 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
         <v>11984000</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>21632</v>
+        <v>21671</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>11984000</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>21632</v>
+        <v>21671</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -33563,7 +33563,7 @@
         </is>
       </c>
       <c r="E526" s="4" t="n">
-        <v>1523</v>
+        <v>1469</v>
       </c>
       <c r="F526" s="3" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>55284900</v>
       </c>
       <c r="I526" s="5" t="n">
-        <v>36300</v>
+        <v>37634</v>
       </c>
       <c r="J526" s="3" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>55284900</v>
       </c>
       <c r="L526" s="5" t="n">
-        <v>36300</v>
+        <v>37634</v>
       </c>
       <c r="M526" s="3" t="inlineStr">
         <is>
@@ -37511,10 +37511,10 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 2088呎 (4+房)
+          <t>A | 2034呎 (4+房)
 $11330万
-$54,264/呎
-(26年-08月-07日)</t>
+$55,704/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -39936,7 +39936,7 @@
           <t>B | 553呎 (2房)
 $1198万
 $21,671/呎
-(26年-08月-10日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -39972,10 +39972,10 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1198万
-$21,632/呎
-(26年-08月-12日)</t>
+$21,671/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -40738,7 +40738,7 @@
           <t>B | 523呎 (2房)
 $1464万
 $28,000/呎
-(26年-08月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -43547,9 +43547,9 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
+          <t>A | 1469呎 (3房)
 $5528万
-$36,300/呎
+$37,634/呎
 (25年-01月-28日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -39078,7 +39078,7 @@
           <t>B | 553呎 (2房)
 $1451万
 $26,247/呎
-(26年-08月-09日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -39796,7 +39796,7 @@
           <t>D | 371呎 (1房)
 $796万
 $21,445/呎
-(26年-08月-09日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -40279,7 +40279,7 @@
           <t>A | 1114呎 (3房)
 $4308万
 $38,671/呎
-(26年-08月-03日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
